--- a/avc/dist/20261025_奇鋐模型_v0.2.1.xlsx
+++ b/avc/dist/20261025_奇鋐模型_v0.2.1.xlsx
@@ -7570,7 +7570,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7788,7 +7788,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7909,7 +7909,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8030,7 +8030,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8151,7 +8151,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8272,7 +8272,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/avc/dist/20261025_奇鋐模型_v0.2.1.xlsx
+++ b/avc/dist/20261025_奇鋐模型_v0.2.1.xlsx
@@ -6047,7 +6047,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6066,7 +6066,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/avc/dist/20261025_奇鋐模型_v0.2.1.xlsx
+++ b/avc/dist/20261025_奇鋐模型_v0.2.1.xlsx
@@ -6351,7 +6351,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -6370,7 +6370,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6953,7 +6953,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -6972,7 +6972,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7169,7 +7169,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -7188,7 +7188,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -40053,7 +40053,7 @@
         <v>32</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>33</v>
@@ -40502,7 +40502,7 @@
         <v>32</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>5.78484809940115</v>
+        <v>5.78484809940116</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>33</v>
@@ -40525,7 +40525,7 @@
         <v>32</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>7.66628721680113</v>
+        <v>7.66628721680114</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>33</v>
@@ -40548,7 +40548,7 @@
         <v>32</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>9.11281373771718</v>
+        <v>9.1128137377172</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>33</v>
@@ -43400,7 +43400,7 @@
       </c>
       <c r="C8" s="19" t="n">
         <f aca="false">PL!D68</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">PL!E68</f>
@@ -43427,7 +43427,7 @@
       </c>
       <c r="C9" s="14" t="n">
         <f aca="false">PL!D72</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="D9" s="14" t="n">
         <f aca="false">PL!E72</f>
@@ -43439,7 +43439,7 @@
       </c>
       <c r="F9" s="14" t="n">
         <f aca="false">PL!G72</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>430</v>
@@ -43458,15 +43458,15 @@
       </c>
       <c r="D10" s="20" t="n">
         <f aca="false">PL!E73/fx</f>
-        <v>5.47981447723099</v>
+        <v>5.479814477231</v>
       </c>
       <c r="E10" s="20" t="n">
         <f aca="false">PL!F73/fx</f>
-        <v>7.92067317636872</v>
+        <v>7.92067317636874</v>
       </c>
       <c r="F10" s="20" t="n">
         <f aca="false">PL!G73/fx</f>
-        <v>8.52162682501696</v>
+        <v>8.52162682501698</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43482,15 +43482,15 @@
       </c>
       <c r="D11" s="20" t="n">
         <f aca="false">PL!E77/fx</f>
-        <v>1.9727572054617</v>
+        <v>1.97275720546171</v>
       </c>
       <c r="E11" s="20" t="n">
         <f aca="false">PL!F77/fx</f>
-        <v>2.16727341048154</v>
+        <v>2.16727341048155</v>
       </c>
       <c r="F11" s="20" t="n">
         <f aca="false">PL!G77/fx</f>
-        <v>2.27895420584109</v>
+        <v>2.2789542058411</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>433</v>
@@ -43509,7 +43509,7 @@
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">PL!E84</f>
-        <v>178.947189172338</v>
+        <v>178.947189172339</v>
       </c>
       <c r="E12" s="18" t="n">
         <f aca="false">PL!F84</f>
@@ -43529,15 +43529,15 @@
       </c>
       <c r="C13" s="19" t="n">
         <f aca="false">PL!D68-PL!D73/fx</f>
-        <v>2.2616840859587</v>
+        <v>2.26168408595869</v>
       </c>
       <c r="D13" s="19" t="n">
         <f aca="false">PL!E68-PL!E73/fx</f>
-        <v>6.08143266593417</v>
+        <v>6.08143266593416</v>
       </c>
       <c r="E13" s="19" t="n">
         <f aca="false">PL!F68-PL!F73/fx</f>
-        <v>9.71865414982553</v>
+        <v>9.71865414982551</v>
       </c>
       <c r="F13" s="19" t="n">
         <f aca="false">PL!G68-PL!G73/fx</f>
@@ -43629,7 +43629,7 @@
       </c>
       <c r="E5" s="19" t="n">
         <f aca="false">E80</f>
-        <v>351.307669196166</v>
+        <v>351.307669196167</v>
       </c>
       <c r="F5" s="19" t="n">
         <f aca="false">F80</f>
@@ -43653,7 +43653,7 @@
       </c>
       <c r="E6" s="14" t="n">
         <f aca="false">E81</f>
-        <v>0.559978344599226</v>
+        <v>0.559978344599227</v>
       </c>
       <c r="F6" s="14" t="n">
         <f aca="false">F81</f>
@@ -43685,7 +43685,7 @@
       </c>
       <c r="F7" s="19" t="n">
         <f aca="false">F73</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="G7" s="19" t="n">
         <f aca="false">G73</f>
@@ -43709,15 +43709,15 @@
       </c>
       <c r="E8" s="19" t="n">
         <f aca="false">E77</f>
-        <v>63.1282305747745</v>
+        <v>63.1282305747746</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">F77</f>
-        <v>69.3527491354094</v>
+        <v>69.3527491354095</v>
       </c>
       <c r="G8" s="19" t="n">
         <f aca="false">G77</f>
-        <v>72.926534586915</v>
+        <v>72.9265345869151</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43877,15 +43877,15 @@
       </c>
       <c r="E14" s="19" t="n">
         <f aca="false">E95</f>
-        <v>68.5879465553677</v>
+        <v>68.5879465553678</v>
       </c>
       <c r="F14" s="19" t="n">
         <f aca="false">F95</f>
-        <v>88.2327362983229</v>
+        <v>88.232736298323</v>
       </c>
       <c r="G14" s="19" t="n">
         <f aca="false">G95</f>
-        <v>94.1437978507718</v>
+        <v>94.1437978507719</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43913,7 +43913,7 @@
       </c>
       <c r="G15" s="15" t="n">
         <f aca="false">G97</f>
-        <v>239.842404408475</v>
+        <v>239.842404408476</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43929,7 +43929,7 @@
       </c>
       <c r="E16" s="14" t="n">
         <f aca="false">E98</f>
-        <v>0.64905357899949</v>
+        <v>0.649053578999492</v>
       </c>
       <c r="F16" s="14" t="n">
         <f aca="false">F98</f>
@@ -43937,7 +43937,7 @@
       </c>
       <c r="G16" s="14" t="n">
         <f aca="false">G98</f>
-        <v>0.0669939729905122</v>
+        <v>0.0669939729905125</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43986,7 +43986,7 @@
       </c>
       <c r="E20" s="14" t="n">
         <f aca="false">E122</f>
-        <v>0.46837151629441</v>
+        <v>0.468371516294412</v>
       </c>
       <c r="F20" s="14" t="n">
         <f aca="false">F122</f>
@@ -44014,7 +44014,7 @@
       </c>
       <c r="E21" s="19" t="n">
         <f aca="false">E114</f>
-        <v>154.724173474757</v>
+        <v>154.724173474758</v>
       </c>
       <c r="F21" s="19" t="n">
         <f aca="false">F114</f>
@@ -44022,7 +44022,7 @@
       </c>
       <c r="G21" s="19" t="n">
         <f aca="false">G114</f>
-        <v>219.588868080437</v>
+        <v>219.588868080438</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44042,11 +44042,11 @@
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">E118</f>
-        <v>63.1282305747745</v>
+        <v>63.1282305747746</v>
       </c>
       <c r="F22" s="19" t="n">
         <f aca="false">F118</f>
-        <v>55.4821993083275</v>
+        <v>55.4821993083276</v>
       </c>
       <c r="G22" s="19" t="n">
         <f aca="false">G118</f>
@@ -44126,7 +44126,7 @@
       </c>
       <c r="E25" s="14" t="n">
         <f aca="false">E123</f>
-        <v>0.46790012245672</v>
+        <v>0.467900122456721</v>
       </c>
       <c r="F25" s="14" t="n">
         <f aca="false">F123</f>
@@ -44134,7 +44134,7 @@
       </c>
       <c r="G25" s="14" t="n">
         <f aca="false">G123</f>
-        <v>0.541530473979294</v>
+        <v>0.541530473979295</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44210,15 +44210,15 @@
       </c>
       <c r="E28" s="19" t="n">
         <f aca="false">E136</f>
-        <v>64.0422292145632</v>
+        <v>64.0422292145633</v>
       </c>
       <c r="F28" s="19" t="n">
         <f aca="false">F136</f>
-        <v>69.6852034444304</v>
+        <v>69.6852034444305</v>
       </c>
       <c r="G28" s="19" t="n">
         <f aca="false">G136</f>
-        <v>80.3243341611877</v>
+        <v>80.3243341611878</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44262,7 +44262,7 @@
       </c>
       <c r="E30" s="14" t="n">
         <f aca="false">E139</f>
-        <v>0.539761322466887</v>
+        <v>0.539761322466888</v>
       </c>
       <c r="F30" s="14" t="n">
         <f aca="false">F139</f>
@@ -44295,7 +44295,7 @@
       </c>
       <c r="E33" s="19" t="n">
         <f aca="false">E162</f>
-        <v>299.73294470458</v>
+        <v>299.732944704581</v>
       </c>
       <c r="F33" s="19" t="n">
         <f aca="false">F162</f>
@@ -44319,11 +44319,11 @@
       </c>
       <c r="E34" s="14" t="n">
         <f aca="false">E163</f>
-        <v>0.330961273837187</v>
+        <v>0.330961273837189</v>
       </c>
       <c r="F34" s="14" t="n">
         <f aca="false">F163</f>
-        <v>-0.0909391746531647</v>
+        <v>-0.0909391746531648</v>
       </c>
       <c r="G34" s="14" t="n">
         <f aca="false">G163</f>
@@ -44375,15 +44375,15 @@
       </c>
       <c r="E36" s="19" t="n">
         <f aca="false">E159</f>
-        <v>63.1282305747745</v>
+        <v>63.1282305747746</v>
       </c>
       <c r="F36" s="19" t="n">
         <f aca="false">F159</f>
-        <v>41.6116494812456</v>
+        <v>41.6116494812457</v>
       </c>
       <c r="G36" s="19" t="n">
         <f aca="false">G159</f>
-        <v>43.755920752149</v>
+        <v>43.7559207521491</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44459,7 +44459,7 @@
       </c>
       <c r="E39" s="14" t="n">
         <f aca="false">E164</f>
-        <v>0.412965411265698</v>
+        <v>0.412965411265699</v>
       </c>
       <c r="F39" s="14" t="n">
         <f aca="false">F164</f>
@@ -44467,7 +44467,7 @@
       </c>
       <c r="G39" s="14" t="n">
         <f aca="false">G164</f>
-        <v>0.435140885762004</v>
+        <v>0.435140885762005</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44515,7 +44515,7 @@
       </c>
       <c r="E41" s="14" t="n">
         <f aca="false">E174</f>
-        <v>0.279501416189205</v>
+        <v>0.279501416189206</v>
       </c>
       <c r="F41" s="14" t="n">
         <f aca="false">F174</f>
@@ -44543,15 +44543,15 @@
       </c>
       <c r="E42" s="19" t="n">
         <f aca="false">E177</f>
-        <v>57.2236532033564</v>
+        <v>57.2236532033565</v>
       </c>
       <c r="F42" s="19" t="n">
         <f aca="false">F177</f>
-        <v>51.1773363557854</v>
+        <v>51.1773363557855</v>
       </c>
       <c r="G42" s="19" t="n">
         <f aca="false">G177</f>
-        <v>56.2426474247612</v>
+        <v>56.2426474247613</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44595,15 +44595,15 @@
       </c>
       <c r="E44" s="14" t="n">
         <f aca="false">E180</f>
-        <v>0.375822937667982</v>
+        <v>0.375822937667983</v>
       </c>
       <c r="F44" s="14" t="n">
         <f aca="false">F180</f>
-        <v>-0.105661147254688</v>
+        <v>-0.105661147254687</v>
       </c>
       <c r="G44" s="14" t="n">
         <f aca="false">G180</f>
-        <v>0.0989756683263405</v>
+        <v>0.0989756683263403</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44683,7 +44683,7 @@
       </c>
       <c r="D63" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E63" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -44806,7 +44806,7 @@
       </c>
       <c r="D68" s="20" t="n">
         <f aca="false">D65*D66*D67/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E68" s="20" t="n">
         <f aca="false">E65*E66*E67/1000</f>
@@ -44854,7 +44854,7 @@
       </c>
       <c r="D70" s="14" t="n">
         <f aca="false">a26_lc/D69</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H70" s="8" t="s">
         <v>468</v>
@@ -44893,7 +44893,7 @@
       </c>
       <c r="D72" s="14" t="n">
         <f aca="false">$D$70*D71</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E72" s="14" t="n">
         <f aca="false">$D$70*E71</f>
@@ -44905,7 +44905,7 @@
       </c>
       <c r="G72" s="14" t="n">
         <f aca="false">$D$70*G71</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44929,7 +44929,7 @@
       </c>
       <c r="F73" s="19" t="n">
         <f aca="false">F69*F72</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="G73" s="19" t="n">
         <f aca="false">G69*G72</f>
@@ -44950,7 +44950,7 @@
       </c>
       <c r="D75" s="22" t="n">
         <f aca="false">a26_air/D65</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44994,15 +44994,15 @@
       </c>
       <c r="E77" s="19" t="n">
         <f aca="false">E65*$D$75*E76</f>
-        <v>63.1282305747745</v>
+        <v>63.1282305747746</v>
       </c>
       <c r="F77" s="19" t="n">
         <f aca="false">F65*$D$75*F76</f>
-        <v>69.3527491354094</v>
+        <v>69.3527491354095</v>
       </c>
       <c r="G77" s="19" t="n">
         <f aca="false">G65*$D$75*G76</f>
-        <v>72.926534586915</v>
+        <v>72.9265345869151</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="E80" s="19" t="n">
         <f aca="false">E73+E77+E78+E79</f>
-        <v>351.307669196166</v>
+        <v>351.307669196167</v>
       </c>
       <c r="F80" s="19" t="n">
         <f aca="false">F73+F77+F78+F79</f>
@@ -45102,7 +45102,7 @@
       </c>
       <c r="E81" s="14" t="n">
         <f aca="false">E80/D80-1</f>
-        <v>0.559978344599226</v>
+        <v>0.559978344599227</v>
       </c>
       <c r="F81" s="14" t="n">
         <f aca="false">F80/E80-1</f>
@@ -45166,7 +45166,7 @@
       </c>
       <c r="G83" s="14" t="n">
         <f aca="false">(G73+G77)/G80</f>
-        <v>0.7360807582572</v>
+        <v>0.736080758257201</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45182,7 +45182,7 @@
       </c>
       <c r="E84" s="18" t="n">
         <f aca="false">(E73+E77)/fx/E65*1000</f>
-        <v>178.947189172338</v>
+        <v>178.947189172339</v>
       </c>
       <c r="F84" s="18" t="n">
         <f aca="false">(F73+F77)/fx/F65*1000</f>
@@ -45238,7 +45238,7 @@
       </c>
       <c r="G87" s="19" t="n">
         <f aca="false">$D$86*G80+d_lc*G73</f>
-        <v>158.548016827002</v>
+        <v>158.548016827003</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45290,7 +45290,7 @@
       </c>
       <c r="F89" s="19" t="n">
         <f aca="false">E89*(1+MAX(0,phi*F81))</f>
-        <v>19.2249952047764</v>
+        <v>19.2249952047765</v>
       </c>
       <c r="G89" s="19" t="n">
         <f aca="false">F89*(1+MAX(0,phi*G81))</f>
@@ -45318,7 +45318,7 @@
       </c>
       <c r="F90" s="19" t="n">
         <f aca="false">F89+0*F80</f>
-        <v>19.2249952047764</v>
+        <v>19.2249952047765</v>
       </c>
       <c r="G90" s="19" t="n">
         <f aca="false">G89+0*G80</f>
@@ -45350,7 +45350,7 @@
       </c>
       <c r="G91" s="19" t="n">
         <f aca="false">G87-G90</f>
-        <v>138.472293112254</v>
+        <v>138.472293112255</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45454,15 +45454,15 @@
       </c>
       <c r="E95" s="19" t="n">
         <f aca="false">(E91+E93)*E94</f>
-        <v>68.5879465553677</v>
+        <v>68.5879465553678</v>
       </c>
       <c r="F95" s="19" t="n">
         <f aca="false">(F91+F93)*F94</f>
-        <v>88.2327362983229</v>
+        <v>88.232736298323</v>
       </c>
       <c r="G95" s="19" t="n">
         <f aca="false">(G91+G93)*G94</f>
-        <v>94.1437978507718</v>
+        <v>94.1437978507719</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45518,7 +45518,7 @@
       </c>
       <c r="G97" s="20" t="n">
         <f aca="false">G95/G96</f>
-        <v>239.842404408475</v>
+        <v>239.842404408476</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45534,7 +45534,7 @@
       </c>
       <c r="E98" s="14" t="n">
         <f aca="false">E97/D97-1</f>
-        <v>0.64905357899949</v>
+        <v>0.649053578999492</v>
       </c>
       <c r="F98" s="14" t="n">
         <f aca="false">F97/E97-1</f>
@@ -45542,7 +45542,7 @@
       </c>
       <c r="G98" s="14" t="n">
         <f aca="false">G97/F97-1</f>
-        <v>0.0669939729905122</v>
+        <v>0.0669939729905125</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45590,7 +45590,7 @@
       </c>
       <c r="D104" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E104" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -45713,7 +45713,7 @@
       </c>
       <c r="D109" s="20" t="n">
         <f aca="false">D106*D107*D108/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E109" s="20" t="n">
         <f aca="false">E106*E107*E108/1000</f>
@@ -45761,7 +45761,7 @@
       </c>
       <c r="D111" s="14" t="n">
         <f aca="false">a26_lc/D110</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H111" s="8" t="s">
         <v>468</v>
@@ -45800,7 +45800,7 @@
       </c>
       <c r="D113" s="14" t="n">
         <f aca="false">$D$111*D112</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E113" s="14" t="n">
         <f aca="false">$D$111*E112</f>
@@ -45812,7 +45812,7 @@
       </c>
       <c r="G113" s="14" t="n">
         <f aca="false">$D$111*G112</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45832,7 +45832,7 @@
       </c>
       <c r="E114" s="19" t="n">
         <f aca="false">E110*E113</f>
-        <v>154.724173474757</v>
+        <v>154.724173474758</v>
       </c>
       <c r="F114" s="19" t="n">
         <f aca="false">F110*F113</f>
@@ -45840,7 +45840,7 @@
       </c>
       <c r="G114" s="19" t="n">
         <f aca="false">G110*G113</f>
-        <v>219.588868080437</v>
+        <v>219.588868080438</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45857,7 +45857,7 @@
       </c>
       <c r="D116" s="22" t="n">
         <f aca="false">a26_air/D106</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45901,11 +45901,11 @@
       </c>
       <c r="E118" s="19" t="n">
         <f aca="false">E106*$D$116*E117</f>
-        <v>63.1282305747745</v>
+        <v>63.1282305747746</v>
       </c>
       <c r="F118" s="19" t="n">
         <f aca="false">F106*$D$116*F117</f>
-        <v>55.4821993083275</v>
+        <v>55.4821993083276</v>
       </c>
       <c r="G118" s="19" t="n">
         <f aca="false">G106*$D$116*G117</f>
@@ -46009,7 +46009,7 @@
       </c>
       <c r="E122" s="14" t="n">
         <f aca="false">E121/D121-1</f>
-        <v>0.46837151629441</v>
+        <v>0.468371516294412</v>
       </c>
       <c r="F122" s="14" t="n">
         <f aca="false">F121/E121-1</f>
@@ -46037,7 +46037,7 @@
       </c>
       <c r="E123" s="14" t="n">
         <f aca="false">E114/E121</f>
-        <v>0.46790012245672</v>
+        <v>0.467900122456721</v>
       </c>
       <c r="F123" s="14" t="n">
         <f aca="false">F114/F121</f>
@@ -46045,7 +46045,7 @@
       </c>
       <c r="G123" s="14" t="n">
         <f aca="false">G114/G121</f>
-        <v>0.541530473979294</v>
+        <v>0.541530473979295</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46145,7 +46145,7 @@
       </c>
       <c r="G128" s="19" t="n">
         <f aca="false">$D$127*G121+d_lc*G114</f>
-        <v>135.968479074339</v>
+        <v>135.96847907434</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46193,7 +46193,7 @@
       </c>
       <c r="E130" s="19" t="n">
         <f aca="false">D130*(1+MAX(0,phi*E122))</f>
-        <v>15.5424159855636</v>
+        <v>15.5424159855637</v>
       </c>
       <c r="F130" s="19" t="n">
         <f aca="false">E130*(1+MAX(0,phi*F122))</f>
@@ -46221,7 +46221,7 @@
       </c>
       <c r="E131" s="19" t="n">
         <f aca="false">E130+0*E121</f>
-        <v>15.5424159855636</v>
+        <v>15.5424159855637</v>
       </c>
       <c r="F131" s="19" t="n">
         <f aca="false">F130+0*F121</f>
@@ -46249,7 +46249,7 @@
       </c>
       <c r="E132" s="19" t="n">
         <f aca="false">E128-E131</f>
-        <v>93.8773766141677</v>
+        <v>93.8773766141678</v>
       </c>
       <c r="F132" s="19" t="n">
         <f aca="false">F128-F131</f>
@@ -46361,15 +46361,15 @@
       </c>
       <c r="E136" s="19" t="n">
         <f aca="false">(E132+E134)*E135</f>
-        <v>64.0422292145632</v>
+        <v>64.0422292145633</v>
       </c>
       <c r="F136" s="19" t="n">
         <f aca="false">(F132+F134)*F135</f>
-        <v>69.6852034444304</v>
+        <v>69.6852034444305</v>
       </c>
       <c r="G136" s="19" t="n">
         <f aca="false">(G132+G134)*G135</f>
-        <v>80.3243341611877</v>
+        <v>80.3243341611878</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46441,7 +46441,7 @@
       </c>
       <c r="E139" s="14" t="n">
         <f aca="false">E138/D138-1</f>
-        <v>0.539761322466887</v>
+        <v>0.539761322466888</v>
       </c>
       <c r="F139" s="14" t="n">
         <f aca="false">F138/E138-1</f>
@@ -46497,7 +46497,7 @@
       </c>
       <c r="D145" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E145" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -46620,7 +46620,7 @@
       </c>
       <c r="D150" s="20" t="n">
         <f aca="false">D147*D148*D149/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E150" s="20" t="n">
         <f aca="false">E147*E148*E149/1000</f>
@@ -46668,7 +46668,7 @@
       </c>
       <c r="D152" s="14" t="n">
         <f aca="false">a26_lc/D151</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H152" s="8" t="s">
         <v>468</v>
@@ -46707,7 +46707,7 @@
       </c>
       <c r="D154" s="14" t="n">
         <f aca="false">$D$152*D153</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E154" s="14" t="n">
         <f aca="false">$D$152*E153</f>
@@ -46719,7 +46719,7 @@
       </c>
       <c r="G154" s="14" t="n">
         <f aca="false">$D$152*G153</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46764,7 +46764,7 @@
       </c>
       <c r="D157" s="22" t="n">
         <f aca="false">a26_air/D147</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46808,15 +46808,15 @@
       </c>
       <c r="E159" s="19" t="n">
         <f aca="false">E147*$D$157*E158</f>
-        <v>63.1282305747745</v>
+        <v>63.1282305747746</v>
       </c>
       <c r="F159" s="19" t="n">
         <f aca="false">F147*$D$157*F158</f>
-        <v>41.6116494812456</v>
+        <v>41.6116494812457</v>
       </c>
       <c r="G159" s="19" t="n">
         <f aca="false">G147*$D$157*G158</f>
-        <v>43.755920752149</v>
+        <v>43.7559207521491</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46892,7 +46892,7 @@
       </c>
       <c r="E162" s="19" t="n">
         <f aca="false">E155+E159+E160+E161</f>
-        <v>299.73294470458</v>
+        <v>299.732944704581</v>
       </c>
       <c r="F162" s="19" t="n">
         <f aca="false">F155+F159+F160+F161</f>
@@ -46916,11 +46916,11 @@
       </c>
       <c r="E163" s="14" t="n">
         <f aca="false">E162/D162-1</f>
-        <v>0.330961273837187</v>
+        <v>0.330961273837189</v>
       </c>
       <c r="F163" s="14" t="n">
         <f aca="false">F162/E162-1</f>
-        <v>-0.0909391746531647</v>
+        <v>-0.0909391746531648</v>
       </c>
       <c r="G163" s="14" t="n">
         <f aca="false">G162/F162-1</f>
@@ -46944,7 +46944,7 @@
       </c>
       <c r="E164" s="14" t="n">
         <f aca="false">E155/E162</f>
-        <v>0.412965411265698</v>
+        <v>0.412965411265699</v>
       </c>
       <c r="F164" s="14" t="n">
         <f aca="false">F155/F162</f>
@@ -46952,7 +46952,7 @@
       </c>
       <c r="G164" s="14" t="n">
         <f aca="false">G155/G162</f>
-        <v>0.435140885762004</v>
+        <v>0.435140885762005</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46976,7 +46976,7 @@
       </c>
       <c r="F165" s="14" t="n">
         <f aca="false">(F155+F159)/F162</f>
-        <v>0.563971231919447</v>
+        <v>0.563971231919448</v>
       </c>
       <c r="G165" s="14" t="n">
         <f aca="false">(G155+G159)/G162</f>
@@ -47000,7 +47000,7 @@
       </c>
       <c r="F166" s="18" t="n">
         <f aca="false">(F155+F159)/fx/F147*1000</f>
-        <v>151.605128776264</v>
+        <v>151.605128776265</v>
       </c>
       <c r="G166" s="18" t="n">
         <f aca="false">(G155+G159)/fx/G147*1000</f>
@@ -47044,7 +47044,7 @@
       </c>
       <c r="E169" s="19" t="n">
         <f aca="false">$D$168*E162+d_lc*E155</f>
-        <v>98.1923411633039</v>
+        <v>98.192341163304</v>
       </c>
       <c r="F169" s="19" t="n">
         <f aca="false">$D$168*F162+d_lc*F155</f>
@@ -47052,7 +47052,7 @@
       </c>
       <c r="G169" s="19" t="n">
         <f aca="false">$D$168*G162+d_lc*G155</f>
-        <v>97.6416105917923</v>
+        <v>97.6416105917924</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47156,15 +47156,15 @@
       </c>
       <c r="E173" s="19" t="n">
         <f aca="false">E169-E172</f>
-        <v>83.775782523491</v>
+        <v>83.7757825234911</v>
       </c>
       <c r="F173" s="19" t="n">
         <f aca="false">F169-F172</f>
-        <v>74.8182760826451</v>
+        <v>74.8182760826452</v>
       </c>
       <c r="G173" s="19" t="n">
         <f aca="false">G169-G172</f>
-        <v>82.3224406292759</v>
+        <v>82.322440629276</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47184,7 +47184,7 @@
       </c>
       <c r="E174" s="14" t="n">
         <f aca="false">E173/E162</f>
-        <v>0.279501416189205</v>
+        <v>0.279501416189206</v>
       </c>
       <c r="F174" s="14" t="n">
         <f aca="false">F173/F162</f>
@@ -47268,15 +47268,15 @@
       </c>
       <c r="E177" s="19" t="n">
         <f aca="false">(E173+E175)*E176</f>
-        <v>57.2236532033564</v>
+        <v>57.2236532033565</v>
       </c>
       <c r="F177" s="19" t="n">
         <f aca="false">(F173+F175)*F176</f>
-        <v>51.1773363557854</v>
+        <v>51.1773363557855</v>
       </c>
       <c r="G177" s="19" t="n">
         <f aca="false">(G173+G175)*G176</f>
-        <v>56.2426474247612</v>
+        <v>56.2426474247613</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47348,15 +47348,15 @@
       </c>
       <c r="E180" s="14" t="n">
         <f aca="false">E179/D179-1</f>
-        <v>0.375822937667982</v>
+        <v>0.375822937667983</v>
       </c>
       <c r="F180" s="14" t="n">
         <f aca="false">F179/E179-1</f>
-        <v>-0.105661147254688</v>
+        <v>-0.105661147254687</v>
       </c>
       <c r="G180" s="14" t="n">
         <f aca="false">G179/F179-1</f>
-        <v>0.0989756683263405</v>
+        <v>0.0989756683263403</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47421,7 +47421,7 @@
       </c>
       <c r="E186" s="19" t="n">
         <f aca="false">E80</f>
-        <v>351.307669196166</v>
+        <v>351.307669196167</v>
       </c>
       <c r="F186" s="19" t="n">
         <f aca="false">F80</f>
@@ -47433,11 +47433,11 @@
       </c>
       <c r="H186" s="23" t="n">
         <f aca="false">G186*(1+H187)</f>
-        <v>498.717974184552</v>
+        <v>498.717974184553</v>
       </c>
       <c r="I186" s="23" t="n">
         <f aca="false">H186*(1+I187)</f>
-        <v>529.175670918957</v>
+        <v>529.175670918958</v>
       </c>
       <c r="J186" s="23" t="n">
         <f aca="false">I186*(1+J187)</f>
@@ -47461,7 +47461,7 @@
       </c>
       <c r="E187" s="14" t="n">
         <f aca="false">E186/D186-1</f>
-        <v>0.559978344599226</v>
+        <v>0.559978344599227</v>
       </c>
       <c r="F187" s="14" t="n">
         <f aca="false">F186/E186-1</f>
@@ -47501,23 +47501,23 @@
       </c>
       <c r="E188" s="19" t="n">
         <f aca="false">E95</f>
-        <v>68.5879465553677</v>
+        <v>68.5879465553678</v>
       </c>
       <c r="F188" s="19" t="n">
         <f aca="false">F95</f>
-        <v>88.2327362983229</v>
+        <v>88.232736298323</v>
       </c>
       <c r="G188" s="19" t="n">
         <f aca="false">G95</f>
-        <v>94.1437978507718</v>
+        <v>94.1437978507719</v>
       </c>
       <c r="H188" s="23" t="n">
         <f aca="false">H186*H189</f>
-        <v>99.9942672362556</v>
+        <v>99.9942672362557</v>
       </c>
       <c r="I188" s="23" t="n">
         <f aca="false">I186*I189</f>
-        <v>106.101115644197</v>
+        <v>106.101115644198</v>
       </c>
       <c r="J188" s="23" t="n">
         <f aca="false">J186*J189</f>
@@ -47632,7 +47632,7 @@
       </c>
       <c r="G191" s="15" t="n">
         <f aca="false">G97</f>
-        <v>239.842404408475</v>
+        <v>239.842404408476</v>
       </c>
       <c r="H191" s="26" t="n">
         <f aca="false">H188/H190</f>
@@ -47661,7 +47661,7 @@
       </c>
       <c r="E192" s="14" t="n">
         <f aca="false">E191/D191-1</f>
-        <v>0.64905357899949</v>
+        <v>0.649053578999492</v>
       </c>
       <c r="F192" s="14" t="n">
         <f aca="false">F191/E191-1</f>
@@ -47669,11 +47669,11 @@
       </c>
       <c r="G192" s="14" t="n">
         <f aca="false">G191/F191-1</f>
-        <v>0.0669939729905122</v>
+        <v>0.0669939729905125</v>
       </c>
       <c r="H192" s="24" t="n">
         <f aca="false">H191/G191-1</f>
-        <v>0.0621439703840867</v>
+        <v>0.0621439703840865</v>
       </c>
       <c r="I192" s="24" t="n">
         <f aca="false">I191/H191-1</f>
@@ -47681,7 +47681,7 @@
       </c>
       <c r="J192" s="24" t="n">
         <f aca="false">J191/I191-1</f>
-        <v>0.0599999999999998</v>
+        <v>0.0600000000000003</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47791,7 +47791,7 @@
       </c>
       <c r="J198" s="23" t="n">
         <f aca="false">I198*(1+J199)</f>
-        <v>500.90168448782</v>
+        <v>500.901684487821</v>
       </c>
       <c r="K198" s="8" t="s">
         <v>495</v>
@@ -47811,7 +47811,7 @@
       </c>
       <c r="E199" s="14" t="n">
         <f aca="false">E198/D198-1</f>
-        <v>0.46837151629441</v>
+        <v>0.468371516294412</v>
       </c>
       <c r="F199" s="14" t="n">
         <f aca="false">F198/E198-1</f>
@@ -47851,27 +47851,27 @@
       </c>
       <c r="E200" s="19" t="n">
         <f aca="false">E136</f>
-        <v>64.0422292145632</v>
+        <v>64.0422292145633</v>
       </c>
       <c r="F200" s="19" t="n">
         <f aca="false">F136</f>
-        <v>69.6852034444304</v>
+        <v>69.6852034444305</v>
       </c>
       <c r="G200" s="19" t="n">
         <f aca="false">G136</f>
-        <v>80.3243341611877</v>
+        <v>80.3243341611878</v>
       </c>
       <c r="H200" s="23" t="n">
         <f aca="false">H198*H201</f>
-        <v>85.926614229251</v>
+        <v>85.9266142292511</v>
       </c>
       <c r="I200" s="23" t="n">
         <f aca="false">I198*I201</f>
-        <v>89.0462520408156</v>
+        <v>89.0462520408157</v>
       </c>
       <c r="J200" s="23" t="n">
         <f aca="false">J198*J201</f>
-        <v>89.3006699037893</v>
+        <v>89.3006699037894</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47986,7 +47986,7 @@
       </c>
       <c r="H203" s="26" t="n">
         <f aca="false">H200/H202</f>
-        <v>218.908162087218</v>
+        <v>218.908162087219</v>
       </c>
       <c r="I203" s="26" t="n">
         <f aca="false">I200/I202</f>
@@ -48011,7 +48011,7 @@
       </c>
       <c r="E204" s="14" t="n">
         <f aca="false">E203/D203-1</f>
-        <v>0.539761322466887</v>
+        <v>0.539761322466888</v>
       </c>
       <c r="F204" s="14" t="n">
         <f aca="false">F203/E203-1</f>
@@ -48027,7 +48027,7 @@
       </c>
       <c r="I204" s="24" t="n">
         <f aca="false">I203/H203-1</f>
-        <v>0.0363058388782946</v>
+        <v>0.0363058388782949</v>
       </c>
       <c r="J204" s="24" t="n">
         <f aca="false">J203/I203-1</f>
@@ -48121,7 +48121,7 @@
       </c>
       <c r="E210" s="19" t="n">
         <f aca="false">E162</f>
-        <v>299.73294470458</v>
+        <v>299.732944704581</v>
       </c>
       <c r="F210" s="19" t="n">
         <f aca="false">F162</f>
@@ -48141,7 +48141,7 @@
       </c>
       <c r="J210" s="23" t="n">
         <f aca="false">I210*(1+J211)</f>
-        <v>336.786393374535</v>
+        <v>336.786393374536</v>
       </c>
       <c r="K210" s="8" t="s">
         <v>495</v>
@@ -48161,11 +48161,11 @@
       </c>
       <c r="E211" s="14" t="n">
         <f aca="false">E210/D210-1</f>
-        <v>0.330961273837187</v>
+        <v>0.330961273837189</v>
       </c>
       <c r="F211" s="14" t="n">
         <f aca="false">F210/E210-1</f>
-        <v>-0.0909391746531647</v>
+        <v>-0.0909391746531648</v>
       </c>
       <c r="G211" s="14" t="n">
         <f aca="false">G210/F210-1</f>
@@ -48201,15 +48201,15 @@
       </c>
       <c r="E212" s="19" t="n">
         <f aca="false">E177</f>
-        <v>57.2236532033564</v>
+        <v>57.2236532033565</v>
       </c>
       <c r="F212" s="19" t="n">
         <f aca="false">F177</f>
-        <v>51.1773363557854</v>
+        <v>51.1773363557855</v>
       </c>
       <c r="G212" s="19" t="n">
         <f aca="false">G177</f>
-        <v>56.2426474247612</v>
+        <v>56.2426474247613</v>
       </c>
       <c r="H212" s="23" t="n">
         <f aca="false">H210*H213</f>
@@ -48344,7 +48344,7 @@
       </c>
       <c r="J215" s="26" t="n">
         <f aca="false">J212/J214</f>
-        <v>130.05079978759</v>
+        <v>130.050799787591</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48361,27 +48361,27 @@
       </c>
       <c r="E216" s="14" t="n">
         <f aca="false">E215/D215-1</f>
-        <v>0.375822937667982</v>
+        <v>0.375822937667983</v>
       </c>
       <c r="F216" s="14" t="n">
         <f aca="false">F215/E215-1</f>
-        <v>-0.105661147254688</v>
+        <v>-0.105661147254687</v>
       </c>
       <c r="G216" s="14" t="n">
         <f aca="false">G215/F215-1</f>
-        <v>0.0989756683263405</v>
+        <v>0.0989756683263403</v>
       </c>
       <c r="H216" s="24" t="n">
         <f aca="false">H215/G215-1</f>
-        <v>-0.00479169153843584</v>
+        <v>-0.00479169153843606</v>
       </c>
       <c r="I216" s="24" t="n">
         <f aca="false">I215/H215-1</f>
-        <v>-0.0313632139030488</v>
+        <v>-0.0313632139030483</v>
       </c>
       <c r="J216" s="24" t="n">
         <f aca="false">J215/I215-1</f>
-        <v>-0.0584615384615383</v>
+        <v>-0.0584615384615387</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48535,7 +48535,7 @@
       </c>
       <c r="D9" s="17" t="n">
         <f aca="false">px/PL!F43</f>
-        <v>24.1217446847802</v>
+        <v>24.1217446847801</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48548,7 +48548,7 @@
       </c>
       <c r="C10" s="17" t="n">
         <f aca="false">px/PL!G29</f>
-        <v>15.3687752797816</v>
+        <v>15.3687752797815</v>
       </c>
       <c r="D10" s="17" t="n">
         <f aca="false">px/PL!G43</f>
@@ -48729,7 +48729,7 @@
       </c>
       <c r="F23" s="30" t="n">
         <f aca="false">E23/px-1</f>
-        <v>-0.292166954313207</v>
+        <v>-0.292166954313206</v>
       </c>
       <c r="G23" s="28" t="n">
         <f aca="false">px/C23</f>
@@ -48758,7 +48758,7 @@
       </c>
       <c r="F24" s="30" t="n">
         <f aca="false">E24/px-1</f>
-        <v>-0.339079117627143</v>
+        <v>-0.339079117627142</v>
       </c>
       <c r="G24" s="28" t="n">
         <f aca="false">px/C24</f>
@@ -48787,7 +48787,7 @@
       </c>
       <c r="F25" s="30" t="n">
         <f aca="false">E25/px-1</f>
-        <v>-0.485004725154184</v>
+        <v>-0.485004725154183</v>
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">px/C25</f>
@@ -48826,7 +48826,7 @@
       </c>
       <c r="C28" s="17" t="n">
         <f aca="false">px*A28/PL!F43</f>
-        <v>24.1217446847802</v>
+        <v>24.1217446847801</v>
       </c>
       <c r="D28" s="17" t="n">
         <f aca="false">pe_mid</f>
@@ -48885,11 +48885,11 @@
       </c>
       <c r="B31" s="17" t="n">
         <f aca="false">px*A31/PL!F15</f>
-        <v>20.986881281469</v>
+        <v>20.9868812814689</v>
       </c>
       <c r="C31" s="17" t="n">
         <f aca="false">px*A31/PL!F43</f>
-        <v>36.1826170271703</v>
+        <v>36.1826170271702</v>
       </c>
       <c r="D31" s="17" t="n">
         <f aca="false">pe_mid</f>
@@ -48906,7 +48906,7 @@
       </c>
       <c r="B32" s="17" t="n">
         <f aca="false">px*A32/PL!F15</f>
-        <v>27.982508375292</v>
+        <v>27.9825083752919</v>
       </c>
       <c r="C32" s="17" t="n">
         <f aca="false">px*A32/PL!F43</f>
@@ -49227,11 +49227,11 @@
       </c>
       <c r="F68" s="19" t="n">
         <f aca="false">C68*E68</f>
-        <v>1941.31546763657</v>
+        <v>1941.31546763658</v>
       </c>
       <c r="G68" s="14" t="n">
         <f aca="false">F68/px-1</f>
-        <v>-0.382729581037655</v>
+        <v>-0.382729581037654</v>
       </c>
       <c r="H68" s="15" t="n">
         <f aca="false">px/E68</f>
@@ -49262,7 +49262,7 @@
       </c>
       <c r="G69" s="14" t="n">
         <f aca="false">F69/px-1</f>
-        <v>-0.292166954313207</v>
+        <v>-0.292166954313206</v>
       </c>
       <c r="H69" s="15" t="n">
         <f aca="false">px/E69</f>
@@ -49293,7 +49293,7 @@
       </c>
       <c r="G70" s="14" t="n">
         <f aca="false">F70/px-1</f>
-        <v>0.207316490013659</v>
+        <v>0.207316490013661</v>
       </c>
       <c r="H70" s="15" t="n">
         <f aca="false">px/E70</f>
@@ -49472,7 +49472,7 @@
       </c>
       <c r="B91" s="15" t="n">
         <f aca="false">PL!G191</f>
-        <v>239.842404408475</v>
+        <v>239.842404408476</v>
       </c>
       <c r="C91" s="15" t="n">
         <f aca="false">PL!G203</f>
@@ -49493,7 +49493,7 @@
       </c>
       <c r="C92" s="15" t="n">
         <f aca="false">PL!H203</f>
-        <v>218.908162087218</v>
+        <v>218.908162087219</v>
       </c>
       <c r="D92" s="15" t="n">
         <f aca="false">PL!H215</f>
@@ -49531,7 +49531,7 @@
       </c>
       <c r="D94" s="15" t="n">
         <f aca="false">PL!J215</f>
-        <v>130.05079978759</v>
+        <v>130.050799787591</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49557,7 +49557,7 @@
       </c>
       <c r="B97" s="15" t="n">
         <f aca="false">B89*(1-$B$96)</f>
-        <v>155.272110098937</v>
+        <v>155.272110098938</v>
       </c>
       <c r="C97" s="15" t="n">
         <f aca="false">C89*(1-$B$96)</f>
@@ -49578,7 +49578,7 @@
       </c>
       <c r="C98" s="15" t="n">
         <f aca="false">C90*(1-$B$96)</f>
-        <v>157.756123705436</v>
+        <v>157.756123705437</v>
       </c>
       <c r="D98" s="15" t="n">
         <f aca="false">D90*(1-$B$96)</f>
@@ -49595,7 +49595,7 @@
       </c>
       <c r="C99" s="15" t="n">
         <f aca="false">C91*(1-$B$96)</f>
-        <v>181.841409225331</v>
+        <v>181.841409225332</v>
       </c>
       <c r="D99" s="15" t="n">
         <f aca="false">D91*(1-$B$96)</f>
@@ -49608,7 +49608,7 @@
       </c>
       <c r="B100" s="15" t="n">
         <f aca="false">B92*(1-$B$96)</f>
-        <v>226.370982823298</v>
+        <v>226.370982823299</v>
       </c>
       <c r="C100" s="15" t="n">
         <f aca="false">C92*(1-$B$96)</f>
@@ -49650,7 +49650,7 @@
       </c>
       <c r="D102" s="15" t="n">
         <f aca="false">D94*(1-$B$96)</f>
-        <v>115.564495160735</v>
+        <v>115.564495160736</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49679,7 +49679,7 @@
       </c>
       <c r="B104" s="18" t="n">
         <f aca="false">B103*(1+tp_r)</f>
-        <v>3745.4697247293</v>
+        <v>3745.46972472931</v>
       </c>
       <c r="C104" s="18" t="n">
         <f aca="false">C103*(1+tp_r)</f>
@@ -49687,7 +49687,7 @@
       </c>
       <c r="D104" s="18" t="n">
         <f aca="false">D103*(1+tp_r)</f>
-        <v>1834.66717881608</v>
+        <v>1834.66717881609</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49867,7 +49867,7 @@
       </c>
       <c r="B119" s="29" t="n">
         <f aca="false">tp_w_dcf*B105+(1-tp_w_dcf)*B115</f>
-        <v>3965.52216912282</v>
+        <v>3965.52216912283</v>
       </c>
       <c r="E119" s="8" t="s">
         <v>656</v>
@@ -49903,7 +49903,7 @@
       </c>
       <c r="B122" s="14" t="n">
         <f aca="false">B119/px-1</f>
-        <v>0.26089735107244</v>
+        <v>0.260897351072441</v>
       </c>
       <c r="E122" s="4" t="s">
         <v>661</v>
@@ -49915,7 +49915,7 @@
       </c>
       <c r="B123" s="14" t="n">
         <f aca="false">B120/px-1</f>
-        <v>0.567106440345038</v>
+        <v>0.56710644034504</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49924,7 +49924,7 @@
       </c>
       <c r="B124" s="14" t="n">
         <f aca="false">B114/cons_feps-1</f>
-        <v>0.350791262974911</v>
+        <v>0.350791262974912</v>
       </c>
       <c r="E124" s="4" t="s">
         <v>664</v>
@@ -50319,11 +50319,11 @@
       </c>
       <c r="C9" s="19" t="n">
         <f aca="false">PL!E80</f>
-        <v>351.307669196166</v>
+        <v>351.307669196167</v>
       </c>
       <c r="D9" s="14" t="n">
         <f aca="false">C9/B9-1</f>
-        <v>0.12637240719146</v>
+        <v>0.126372407191462</v>
       </c>
       <c r="E9" s="19" t="n">
         <f aca="false">PL!E121</f>
@@ -50331,15 +50331,15 @@
       </c>
       <c r="F9" s="14" t="n">
         <f aca="false">E9/B9-1</f>
-        <v>0.0602282814924731</v>
+        <v>0.0602282814924739</v>
       </c>
       <c r="G9" s="19" t="n">
         <f aca="false">PL!E162</f>
-        <v>299.73294470458</v>
+        <v>299.732944704581</v>
       </c>
       <c r="H9" s="14" t="n">
         <f aca="false">G9/B9-1</f>
-        <v>-0.0389879070560084</v>
+        <v>-0.0389879070560075</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>690</v>
@@ -50359,7 +50359,7 @@
       </c>
       <c r="D10" s="14" t="n">
         <f aca="false">C10/B10-1</f>
-        <v>0.128930518631988</v>
+        <v>0.128930518631989</v>
       </c>
       <c r="E10" s="20" t="n">
         <f aca="false">PL!E138</f>
@@ -50367,7 +50367,7 @@
       </c>
       <c r="F10" s="14" t="n">
         <f aca="false">E10/B10-1</f>
-        <v>0.0541098060601923</v>
+        <v>0.0541098060601932</v>
       </c>
       <c r="G10" s="20" t="n">
         <f aca="false">PL!E179</f>
@@ -50375,7 +50375,7 @@
       </c>
       <c r="H10" s="14" t="n">
         <f aca="false">G10/B10-1</f>
-        <v>-0.0581212627975015</v>
+        <v>-0.0581212627975006</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>693</v>
@@ -50395,7 +50395,7 @@
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">C11/B11-1</f>
-        <v>0.0918944302559464</v>
+        <v>0.0918944302559477</v>
       </c>
       <c r="E11" s="20" t="n">
         <f aca="false">PL!E138</f>
@@ -50403,7 +50403,7 @@
       </c>
       <c r="F11" s="14" t="n">
         <f aca="false">E11/B11-1</f>
-        <v>0.0195283120789638</v>
+        <v>0.0195283120789647</v>
       </c>
       <c r="G11" s="20" t="n">
         <f aca="false">PL!E179</f>
@@ -50411,7 +50411,7 @@
       </c>
       <c r="H11" s="14" t="n">
         <f aca="false">G11/B11-1</f>
-        <v>-0.0890208651865105</v>
+        <v>-0.0890208651865097</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>690</v>
@@ -50431,7 +50431,7 @@
       </c>
       <c r="D12" s="14" t="n">
         <f aca="false">C12/B12-1</f>
-        <v>0.213527784386826</v>
+        <v>0.213527784386828</v>
       </c>
       <c r="E12" s="20" t="n">
         <f aca="false">PL!E138</f>
@@ -50439,7 +50439,7 @@
       </c>
       <c r="F12" s="14" t="n">
         <f aca="false">E12/B12-1</f>
-        <v>0.133100324897538</v>
+        <v>0.133100324897539</v>
       </c>
       <c r="G12" s="20" t="n">
         <f aca="false">PL!E179</f>
@@ -50447,7 +50447,7 @@
       </c>
       <c r="H12" s="14" t="n">
         <f aca="false">G12/B12-1</f>
-        <v>0.0124591356636066</v>
+        <v>0.0124591356636075</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>701</v>
@@ -50467,7 +50467,7 @@
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">C13/B13-1</f>
-        <v>0.252317535109719</v>
+        <v>0.25231753510972</v>
       </c>
       <c r="E13" s="20" t="n">
         <f aca="false">PL!E138</f>
@@ -50475,7 +50475,7 @@
       </c>
       <c r="F13" s="14" t="n">
         <f aca="false">E13/B13-1</f>
-        <v>0.169319255944933</v>
+        <v>0.169319255944934</v>
       </c>
       <c r="G13" s="20" t="n">
         <f aca="false">PL!E179</f>
@@ -50483,7 +50483,7 @@
       </c>
       <c r="H13" s="14" t="n">
         <f aca="false">G13/B13-1</f>
-        <v>0.0448218371977547</v>
+        <v>0.0448218371977558</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>701</v>
@@ -50503,7 +50503,7 @@
       </c>
       <c r="D14" s="14" t="n">
         <f aca="false">C14/B14-1</f>
-        <v>0.140499090619797</v>
+        <v>0.140499090619798</v>
       </c>
       <c r="E14" s="20" t="n">
         <f aca="false">PL!E138</f>
@@ -50511,7 +50511,7 @@
       </c>
       <c r="F14" s="14" t="n">
         <f aca="false">E14/B14-1</f>
-        <v>0.0649116623066155</v>
+        <v>0.0649116623066164</v>
       </c>
       <c r="G14" s="20" t="n">
         <f aca="false">PL!E179</f>
@@ -50519,7 +50519,7 @@
       </c>
       <c r="H14" s="14" t="n">
         <f aca="false">G14/B14-1</f>
-        <v>-0.0484694801631571</v>
+        <v>-0.0484694801631561</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>701</v>
@@ -50542,7 +50542,7 @@
       </c>
       <c r="D15" s="14" t="n">
         <f aca="false">C15/B15-1</f>
-        <v>0.151671684885176</v>
+        <v>0.151671684885178</v>
       </c>
       <c r="E15" s="20" t="n">
         <f aca="false">PL!F138</f>
@@ -50550,7 +50550,7 @@
       </c>
       <c r="F15" s="14" t="n">
         <f aca="false">E15/B15-1</f>
-        <v>-0.0904229084422159</v>
+        <v>-0.0904229084422151</v>
       </c>
       <c r="G15" s="20" t="n">
         <f aca="false">PL!F179</f>
@@ -50625,23 +50625,23 @@
       </c>
       <c r="D18" s="14" t="n">
         <f aca="false">C18-B18</f>
-        <v>-0.000853301402093831</v>
+        <v>-0.000853301402093554</v>
       </c>
       <c r="E18" s="14" t="n">
         <f aca="false">PL!E123</f>
-        <v>0.46790012245672</v>
+        <v>0.467900122456721</v>
       </c>
       <c r="F18" s="14" t="n">
         <f aca="false">E18-B18</f>
-        <v>-0.0320998775432795</v>
+        <v>-0.0320998775432793</v>
       </c>
       <c r="G18" s="14" t="n">
         <f aca="false">PL!E164</f>
-        <v>0.412965411265698</v>
+        <v>0.412965411265699</v>
       </c>
       <c r="H18" s="14" t="n">
         <f aca="false">G18-B18</f>
-        <v>-0.0870345887343016</v>
+        <v>-0.0870345887343014</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>690</v>
@@ -50728,15 +50728,15 @@
       </c>
       <c r="C21" s="14" t="n">
         <f aca="false">PL!D70</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E21" s="14" t="n">
         <f aca="false">PL!D111</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="G21" s="14" t="n">
         <f aca="false">PL!D152</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>118</v>
@@ -50751,7 +50751,7 @@
       </c>
       <c r="C22" s="14" t="n">
         <f aca="false">(dlc_27+PL!E73/fx)/PL!E68</f>
-        <v>0.974346663222371</v>
+        <v>0.974346663222373</v>
       </c>
       <c r="E22" s="14" t="n">
         <f aca="false">(dlc_27+PL!E114/fx)/PL!E109</f>
@@ -50759,7 +50759,7 @@
       </c>
       <c r="G22" s="14" t="n">
         <f aca="false">(dlc_27+PL!E155/fx)/PL!E150</f>
-        <v>1.18283224828967</v>
+        <v>1.18283224828968</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>718</v>
@@ -50774,15 +50774,15 @@
       </c>
       <c r="C23" s="14" t="n">
         <f aca="false">(dlc_26+PL!D73/fx)/PL!D68</f>
-        <v>1.15355444084619</v>
+        <v>1.1535544408462</v>
       </c>
       <c r="E23" s="14" t="n">
         <f aca="false">(dlc_26+PL!D114/fx)/PL!D109</f>
-        <v>1.15355444084619</v>
+        <v>1.1535544408462</v>
       </c>
       <c r="G23" s="14" t="n">
         <f aca="false">(dlc_26+PL!D155/fx)/PL!D150</f>
-        <v>1.15355444084619</v>
+        <v>1.1535544408462</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>38</v>
@@ -50794,7 +50794,7 @@
       </c>
       <c r="C24" s="18" t="n">
         <f aca="false">PL!E84</f>
-        <v>178.947189172338</v>
+        <v>178.947189172339</v>
       </c>
       <c r="E24" s="18" t="n">
         <f aca="false">PL!E125</f>
@@ -50886,7 +50886,7 @@
       </c>
       <c r="H28" s="14" t="n">
         <f aca="false">G28-B28</f>
-        <v>0.00557792467594198</v>
+        <v>0.00557792467594204</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>728</v>
@@ -50950,7 +50950,7 @@
       </c>
       <c r="D34" s="14" t="n">
         <f aca="false">C34/B34-1</f>
-        <v>0.350791262974911</v>
+        <v>0.350791262974912</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>346</v>
@@ -50969,11 +50969,11 @@
       </c>
       <c r="C35" s="15" t="n">
         <f aca="false">Val!B119</f>
-        <v>3965.52216912282</v>
+        <v>3965.52216912283</v>
       </c>
       <c r="D35" s="14" t="n">
         <f aca="false">C35/B35-1</f>
-        <v>-0.0398251406482268</v>
+        <v>-0.0398251406482256</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>342</v>
@@ -50996,7 +50996,7 @@
       </c>
       <c r="D36" s="14" t="n">
         <f aca="false">C36/B36-1</f>
-        <v>0.19335345154604</v>
+        <v>0.193353451546041</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>38</v>
@@ -51081,7 +51081,7 @@
       </c>
       <c r="C4" s="19" t="n">
         <f aca="false">PL!E80</f>
-        <v>351.307669196166</v>
+        <v>351.307669196167</v>
       </c>
       <c r="D4" s="19" t="n">
         <f aca="false">PL!E73</f>
@@ -51105,7 +51105,7 @@
       </c>
       <c r="I4" s="19" t="n">
         <f aca="false">PL!F73</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="J4" s="14" t="n">
         <f aca="false">PL!F88</f>
@@ -51133,7 +51133,7 @@
       </c>
       <c r="D5" s="19" t="n">
         <f aca="false">E53</f>
-        <v>156.895740821771</v>
+        <v>156.895740821772</v>
       </c>
       <c r="E5" s="14" t="n">
         <f aca="false">E68</f>
@@ -51145,7 +51145,7 @@
       </c>
       <c r="G5" s="14" t="n">
         <f aca="false">F5/F$4-1</f>
-        <v>-0.059299351896055</v>
+        <v>-0.0592993518960551</v>
       </c>
       <c r="H5" s="19" t="n">
         <f aca="false">F60</f>
@@ -51177,7 +51177,7 @@
       </c>
       <c r="C6" s="19" t="n">
         <f aca="false">E101</f>
-        <v>369.765991645786</v>
+        <v>369.765991645787</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">E94</f>
@@ -51197,7 +51197,7 @@
       </c>
       <c r="H6" s="19" t="n">
         <f aca="false">F101</f>
-        <v>483.865028099875</v>
+        <v>483.865028099876</v>
       </c>
       <c r="I6" s="19" t="n">
         <f aca="false">F94</f>
@@ -51249,7 +51249,7 @@
       </c>
       <c r="I7" s="19" t="n">
         <f aca="false">F135</f>
-        <v>181.043958316999</v>
+        <v>181.043958317</v>
       </c>
       <c r="J7" s="14" t="n">
         <f aca="false">F150</f>
@@ -51273,7 +51273,7 @@
       </c>
       <c r="C8" s="19" t="n">
         <f aca="false">E183</f>
-        <v>391.773991489564</v>
+        <v>391.773991489565</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">E176</f>
@@ -51293,7 +51293,7 @@
       </c>
       <c r="H8" s="19" t="n">
         <f aca="false">F183</f>
-        <v>514.039021152708</v>
+        <v>514.039021152709</v>
       </c>
       <c r="I8" s="19" t="n">
         <f aca="false">F176</f>
@@ -51333,11 +51333,11 @@
       </c>
       <c r="F9" s="15" t="n">
         <f aca="false">E241</f>
-        <v>161.224990800019</v>
+        <v>161.22499080002</v>
       </c>
       <c r="G9" s="14" t="n">
         <f aca="false">F9/F$4-1</f>
-        <v>-0.0773217039428952</v>
+        <v>-0.0773217039428955</v>
       </c>
       <c r="H9" s="19" t="n">
         <f aca="false">F224</f>
@@ -51357,7 +51357,7 @@
       </c>
       <c r="L9" s="14" t="n">
         <f aca="false">K9/K$4-1</f>
-        <v>-0.0633124928545404</v>
+        <v>-0.0633124928545402</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51369,7 +51369,7 @@
       </c>
       <c r="C10" s="19" t="n">
         <f aca="false">E265</f>
-        <v>324.330121000567</v>
+        <v>324.330121000568</v>
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">E258</f>
@@ -51385,11 +51385,11 @@
       </c>
       <c r="G10" s="14" t="n">
         <f aca="false">F10/F$4-1</f>
-        <v>-0.086668283540388</v>
+        <v>-0.0866682835403883</v>
       </c>
       <c r="H10" s="19" t="n">
         <f aca="false">F265</f>
-        <v>402.627354496093</v>
+        <v>402.627354496094</v>
       </c>
       <c r="I10" s="19" t="n">
         <f aca="false">F258</f>
@@ -51417,7 +51417,7 @@
       </c>
       <c r="C11" s="19" t="n">
         <f aca="false">E306</f>
-        <v>338.682023081211</v>
+        <v>338.682023081212</v>
       </c>
       <c r="D11" s="19" t="n">
         <f aca="false">E299</f>
@@ -51433,7 +51433,7 @@
       </c>
       <c r="G11" s="14" t="n">
         <f aca="false">F11/F$4-1</f>
-        <v>-0.0331060236555354</v>
+        <v>-0.0331060236555355</v>
       </c>
       <c r="H11" s="19" t="n">
         <f aca="false">F306</f>
@@ -51441,7 +51441,7 @@
       </c>
       <c r="I11" s="19" t="n">
         <f aca="false">F299</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="J11" s="14" t="n">
         <f aca="false">F314</f>
@@ -51453,7 +51453,7 @@
       </c>
       <c r="L11" s="14" t="n">
         <f aca="false">K11/K$4-1</f>
-        <v>-0.043920255032872</v>
+        <v>-0.0439202550328721</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51477,7 +51477,7 @@
       </c>
       <c r="F12" s="15" t="n">
         <f aca="false">E364</f>
-        <v>180.520675376328</v>
+        <v>180.520675376329</v>
       </c>
       <c r="G12" s="14" t="n">
         <f aca="false">F12/F$4-1</f>
@@ -51485,11 +51485,11 @@
       </c>
       <c r="H12" s="19" t="n">
         <f aca="false">F347</f>
-        <v>462.960745252188</v>
+        <v>462.960745252189</v>
       </c>
       <c r="I12" s="19" t="n">
         <f aca="false">F340</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="J12" s="14" t="n">
         <f aca="false">F355</f>
@@ -51497,11 +51497,11 @@
       </c>
       <c r="K12" s="15" t="n">
         <f aca="false">F364</f>
-        <v>234.660553327016</v>
+        <v>234.660553327017</v>
       </c>
       <c r="L12" s="14" t="n">
         <f aca="false">K12/K$4-1</f>
-        <v>0.0439413193678657</v>
+        <v>0.0439413193678659</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51517,7 +51517,7 @@
       </c>
       <c r="D13" s="19" t="n">
         <f aca="false">E381</f>
-        <v>140.283250617113</v>
+        <v>140.283250617114</v>
       </c>
       <c r="E13" s="14" t="n">
         <f aca="false">E396</f>
@@ -51537,7 +51537,7 @@
       </c>
       <c r="I13" s="19" t="n">
         <f aca="false">F381</f>
-        <v>202.769233315039</v>
+        <v>202.76923331504</v>
       </c>
       <c r="J13" s="14" t="n">
         <f aca="false">F396</f>
@@ -51561,7 +51561,7 @@
       </c>
       <c r="C14" s="19" t="n">
         <f aca="false">E429</f>
-        <v>399.004127965399</v>
+        <v>399.0041279654</v>
       </c>
       <c r="D14" s="19" t="n">
         <f aca="false">E422</f>
@@ -51581,11 +51581,11 @@
       </c>
       <c r="H14" s="19" t="n">
         <f aca="false">F429</f>
-        <v>506.18429598175</v>
+        <v>506.184295981751</v>
       </c>
       <c r="I14" s="19" t="n">
         <f aca="false">F422</f>
-        <v>304.153849972559</v>
+        <v>304.15384997256</v>
       </c>
       <c r="J14" s="14" t="n">
         <f aca="false">F437</f>
@@ -51609,7 +51609,7 @@
       </c>
       <c r="C15" s="19" t="n">
         <f aca="false">E470</f>
-        <v>344.326458346166</v>
+        <v>344.326458346167</v>
       </c>
       <c r="D15" s="19" t="n">
         <f aca="false">E463</f>
@@ -51625,7 +51625,7 @@
       </c>
       <c r="G15" s="14" t="n">
         <f aca="false">F15/F$4-1</f>
-        <v>-0.0183056082389812</v>
+        <v>-0.0183056082389813</v>
       </c>
       <c r="H15" s="19" t="n">
         <f aca="false">F470</f>
@@ -51633,7 +51633,7 @@
       </c>
       <c r="I15" s="19" t="n">
         <f aca="false">F463</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="J15" s="14" t="n">
         <f aca="false">F478</f>
@@ -51645,7 +51645,7 @@
       </c>
       <c r="L15" s="14" t="n">
         <f aca="false">K15/K$4-1</f>
-        <v>-0.0266934703749939</v>
+        <v>-0.0266934703749937</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51673,7 +51673,7 @@
       </c>
       <c r="G16" s="14" t="n">
         <f aca="false">F16/F$4-1</f>
-        <v>0.0174789033507694</v>
+        <v>0.017478903350769</v>
       </c>
       <c r="H16" s="19" t="n">
         <f aca="false">F511</f>
@@ -51681,7 +51681,7 @@
       </c>
       <c r="I16" s="19" t="n">
         <f aca="false">F504</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="J16" s="14" t="n">
         <f aca="false">F519</f>
@@ -51705,7 +51705,7 @@
       </c>
       <c r="C17" s="19" t="n">
         <f aca="false">E552</f>
-        <v>351.307669196166</v>
+        <v>351.307669196167</v>
       </c>
       <c r="D17" s="19" t="n">
         <f aca="false">E545</f>
@@ -51721,7 +51721,7 @@
       </c>
       <c r="G17" s="14" t="n">
         <f aca="false">F17/F$4-1</f>
-        <v>-0.0247749281296963</v>
+        <v>-0.0247749281296965</v>
       </c>
       <c r="H17" s="19" t="n">
         <f aca="false">F552</f>
@@ -51729,7 +51729,7 @@
       </c>
       <c r="I17" s="19" t="n">
         <f aca="false">F545</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="J17" s="14" t="n">
         <f aca="false">F560</f>
@@ -51753,7 +51753,7 @@
       </c>
       <c r="C18" s="19" t="n">
         <f aca="false">E593</f>
-        <v>351.307669196166</v>
+        <v>351.307669196167</v>
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">E586</f>
@@ -51777,7 +51777,7 @@
       </c>
       <c r="I18" s="19" t="n">
         <f aca="false">F586</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="J18" s="14" t="n">
         <f aca="false">F601</f>
@@ -51785,11 +51785,11 @@
       </c>
       <c r="K18" s="15" t="n">
         <f aca="false">F610</f>
-        <v>232.497089783966</v>
+        <v>232.497089783967</v>
       </c>
       <c r="L18" s="14" t="n">
         <f aca="false">K18/K$4-1</f>
-        <v>0.034316655343537</v>
+        <v>0.0343166553435366</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51801,7 +51801,7 @@
       </c>
       <c r="C19" s="19" t="n">
         <f aca="false">E634</f>
-        <v>351.307669196166</v>
+        <v>351.307669196167</v>
       </c>
       <c r="D19" s="19" t="n">
         <f aca="false">E627</f>
@@ -51813,11 +51813,11 @@
       </c>
       <c r="F19" s="15" t="n">
         <f aca="false">E651</f>
-        <v>162.653397652869</v>
+        <v>162.65339765287</v>
       </c>
       <c r="G19" s="14" t="n">
         <f aca="false">F19/F$4-1</f>
-        <v>-0.0691470407314165</v>
+        <v>-0.0691470407314168</v>
       </c>
       <c r="H19" s="19" t="n">
         <f aca="false">F634</f>
@@ -51825,7 +51825,7 @@
       </c>
       <c r="I19" s="19" t="n">
         <f aca="false">F627</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="J19" s="14" t="n">
         <f aca="false">F642</f>
@@ -51837,7 +51837,7 @@
       </c>
       <c r="L19" s="14" t="n">
         <f aca="false">K19/K$4-1</f>
-        <v>-0.0675700387494738</v>
+        <v>-0.0675700387494737</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51865,7 +51865,7 @@
       </c>
       <c r="G20" s="14" t="n">
         <f aca="false">F20/F$4-1</f>
-        <v>-0.0332541062834409</v>
+        <v>-0.0332541062834411</v>
       </c>
       <c r="H20" s="19" t="n">
         <f aca="false">F675</f>
@@ -51873,7 +51873,7 @@
       </c>
       <c r="I20" s="19" t="n">
         <f aca="false">F668</f>
-        <v>221.778848938324</v>
+        <v>221.778848938325</v>
       </c>
       <c r="J20" s="14" t="n">
         <f aca="false">F683</f>
@@ -51885,7 +51885,7 @@
       </c>
       <c r="L20" s="14" t="n">
         <f aca="false">K20/K$4-1</f>
-        <v>-0.0472133120628954</v>
+        <v>-0.0472133120628953</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51913,15 +51913,15 @@
       </c>
       <c r="G21" s="14" t="n">
         <f aca="false">F21/F$4-1</f>
-        <v>0.0246053686139216</v>
+        <v>0.0246053686139214</v>
       </c>
       <c r="H21" s="19" t="n">
         <f aca="false">F716</f>
-        <v>456.345223672391</v>
+        <v>456.345223672392</v>
       </c>
       <c r="I21" s="19" t="n">
         <f aca="false">F709</f>
-        <v>277.223561172905</v>
+        <v>277.223561172906</v>
       </c>
       <c r="J21" s="14" t="n">
         <f aca="false">F724</f>
@@ -51945,7 +51945,7 @@
       </c>
       <c r="C22" s="19" t="n">
         <f aca="false">E757</f>
-        <v>347.290072131241</v>
+        <v>347.290072131242</v>
       </c>
       <c r="D22" s="19" t="n">
         <f aca="false">E750</f>
@@ -51961,15 +51961,15 @@
       </c>
       <c r="G22" s="14" t="n">
         <f aca="false">F22/F$4-1</f>
-        <v>-0.0105346421291078</v>
+        <v>-0.0105346421291082</v>
       </c>
       <c r="H22" s="19" t="n">
         <f aca="false">F757</f>
-        <v>436.550510028372</v>
+        <v>436.550510028373</v>
       </c>
       <c r="I22" s="19" t="n">
         <f aca="false">F750</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="J22" s="14" t="n">
         <f aca="false">F765</f>
@@ -51981,7 +51981,7 @@
       </c>
       <c r="L22" s="14" t="n">
         <f aca="false">K22/K$4-1</f>
-        <v>-0.0104229964191908</v>
+        <v>-0.0104229964191905</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52017,7 +52017,7 @@
       </c>
       <c r="I23" s="19" t="n">
         <f aca="false">F791</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="J23" s="14" t="n">
         <f aca="false">F806</f>
@@ -52045,7 +52045,7 @@
       </c>
       <c r="D24" s="19" t="n">
         <f aca="false">PL!E114</f>
-        <v>154.724173474757</v>
+        <v>154.724173474758</v>
       </c>
       <c r="E24" s="14" t="n">
         <f aca="false">PL!E129</f>
@@ -52057,7 +52057,7 @@
       </c>
       <c r="G24" s="14" t="n">
         <f aca="false">F24/F$4-1</f>
-        <v>-0.0662757462367674</v>
+        <v>-0.0662757462367676</v>
       </c>
       <c r="H24" s="19" t="n">
         <f aca="false">PL!F121</f>
@@ -52089,7 +52089,7 @@
       </c>
       <c r="C25" s="19" t="n">
         <f aca="false">PL!E162</f>
-        <v>299.73294470458</v>
+        <v>299.732944704581</v>
       </c>
       <c r="D25" s="19" t="n">
         <f aca="false">PL!E155</f>
@@ -52178,7 +52178,7 @@
       </c>
       <c r="D43" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E43" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -52301,7 +52301,7 @@
       </c>
       <c r="D48" s="20" t="n">
         <f aca="false">D45*D46*D47/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E48" s="20" t="n">
         <f aca="false">E45*E46*E47/1000</f>
@@ -52349,7 +52349,7 @@
       </c>
       <c r="D50" s="14" t="n">
         <f aca="false">a26_lc/D49</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H50" s="8" t="s">
         <v>468</v>
@@ -52388,19 +52388,19 @@
       </c>
       <c r="D52" s="14" t="n">
         <f aca="false">$D$50*D51</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E52" s="14" t="n">
         <f aca="false">$D$50*E51</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
       <c r="F52" s="14" t="n">
         <f aca="false">$D$50*F51</f>
-        <v>0.374195730837507</v>
+        <v>0.374195730837508</v>
       </c>
       <c r="G52" s="14" t="n">
         <f aca="false">$D$50*G51</f>
-        <v>0.349249348781673</v>
+        <v>0.349249348781674</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52420,7 +52420,7 @@
       </c>
       <c r="E53" s="19" t="n">
         <f aca="false">E49*E52</f>
-        <v>156.895740821771</v>
+        <v>156.895740821772</v>
       </c>
       <c r="F53" s="19" t="n">
         <f aca="false">F49*F52</f>
@@ -52445,7 +52445,7 @@
       </c>
       <c r="D55" s="22" t="n">
         <f aca="false">a26_air/D45</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52489,15 +52489,15 @@
       </c>
       <c r="E57" s="19" t="n">
         <f aca="false">E45*$D$55*E56</f>
-        <v>63.1282305747745</v>
+        <v>63.1282305747746</v>
       </c>
       <c r="F57" s="19" t="n">
         <f aca="false">F45*$D$55*F56</f>
-        <v>69.3527491354094</v>
+        <v>69.3527491354095</v>
       </c>
       <c r="G57" s="19" t="n">
         <f aca="false">G45*$D$55*G56</f>
-        <v>72.926534586915</v>
+        <v>72.9265345869151</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52597,7 +52597,7 @@
       </c>
       <c r="E61" s="14" t="n">
         <f aca="false">E60/D60-1</f>
-        <v>0.478014340326496</v>
+        <v>0.478014340326498</v>
       </c>
       <c r="F61" s="14" t="n">
         <f aca="false">F60/E60-1</f>
@@ -52605,7 +52605,7 @@
       </c>
       <c r="G61" s="14" t="n">
         <f aca="false">G60/F60-1</f>
-        <v>0.0551832898371574</v>
+        <v>0.0551832898371576</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52653,7 +52653,7 @@
       </c>
       <c r="E63" s="14" t="n">
         <f aca="false">(E53+E57)/E60</f>
-        <v>0.661031705626531</v>
+        <v>0.661031705626532</v>
       </c>
       <c r="F63" s="14" t="n">
         <f aca="false">(F53+F57)/F60</f>
@@ -52681,7 +52681,7 @@
       </c>
       <c r="F64" s="18" t="n">
         <f aca="false">(F53+F57)/fx/F45*1000</f>
-        <v>166.082198811988</v>
+        <v>166.082198811989</v>
       </c>
       <c r="G64" s="18" t="n">
         <f aca="false">(G53+G57)/fx/G45*1000</f>
@@ -52725,7 +52725,7 @@
       </c>
       <c r="E67" s="19" t="n">
         <f aca="false">$D$66*E60+d_lc*E53</f>
-        <v>110.207683928603</v>
+        <v>110.207683928604</v>
       </c>
       <c r="F67" s="19" t="n">
         <f aca="false">$D$66*F60+d_lc*F53</f>
@@ -52789,7 +52789,7 @@
       </c>
       <c r="G69" s="19" t="n">
         <f aca="false">F69*(1+MAX(0,phi*G61))</f>
-        <v>18.4949203950311</v>
+        <v>18.4949203950312</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52817,7 +52817,7 @@
       </c>
       <c r="G70" s="19" t="n">
         <f aca="false">G69+0*G60</f>
-        <v>18.4949203950311</v>
+        <v>18.4949203950312</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52837,7 +52837,7 @@
       </c>
       <c r="E71" s="19" t="n">
         <f aca="false">E67-E70</f>
-        <v>94.5862604100047</v>
+        <v>94.5862604100048</v>
       </c>
       <c r="F71" s="19" t="n">
         <f aca="false">F67-F70</f>
@@ -52845,7 +52845,7 @@
       </c>
       <c r="G71" s="19" t="n">
         <f aca="false">G67-G70</f>
-        <v>122.593353636886</v>
+        <v>122.593353636887</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52957,7 +52957,7 @@
       </c>
       <c r="G75" s="19" t="n">
         <f aca="false">(G71+G73)*G74</f>
-        <v>83.4255137048983</v>
+        <v>83.4255137048984</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53029,7 +53029,7 @@
       </c>
       <c r="E78" s="14" t="n">
         <f aca="false">E77/D77-1</f>
-        <v>0.55126577052295</v>
+        <v>0.551265770522952</v>
       </c>
       <c r="F78" s="14" t="n">
         <f aca="false">F77/E77-1</f>
@@ -53037,7 +53037,7 @@
       </c>
       <c r="G78" s="14" t="n">
         <f aca="false">G77/F77-1</f>
-        <v>0.0581059860444275</v>
+        <v>0.0581059860444273</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53085,7 +53085,7 @@
       </c>
       <c r="D84" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E84" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -53208,7 +53208,7 @@
       </c>
       <c r="D89" s="20" t="n">
         <f aca="false">D86*D87*D88/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E89" s="20" t="n">
         <f aca="false">E86*E87*E88/1000</f>
@@ -53256,7 +53256,7 @@
       </c>
       <c r="D91" s="14" t="n">
         <f aca="false">a26_lc/D90</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H91" s="8" t="s">
         <v>468</v>
@@ -53295,19 +53295,19 @@
       </c>
       <c r="D93" s="14" t="n">
         <f aca="false">$D$91*D92</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E93" s="14" t="n">
         <f aca="false">$D$91*E92</f>
-        <v>0.52387402317251</v>
+        <v>0.523874023172511</v>
       </c>
       <c r="F93" s="14" t="n">
         <f aca="false">$D$91*F92</f>
-        <v>0.52387402317251</v>
+        <v>0.523874023172511</v>
       </c>
       <c r="G93" s="14" t="n">
         <f aca="false">$D$91*G92</f>
-        <v>0.52387402317251</v>
+        <v>0.523874023172511</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53352,7 +53352,7 @@
       </c>
       <c r="D96" s="22" t="n">
         <f aca="false">a26_air/D86</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53396,15 +53396,15 @@
       </c>
       <c r="E98" s="19" t="n">
         <f aca="false">E86*$D$96*E97</f>
-        <v>63.1282305747745</v>
+        <v>63.1282305747746</v>
       </c>
       <c r="F98" s="19" t="n">
         <f aca="false">F86*$D$96*F97</f>
-        <v>69.3527491354094</v>
+        <v>69.3527491354095</v>
       </c>
       <c r="G98" s="19" t="n">
         <f aca="false">G86*$D$96*G97</f>
-        <v>72.926534586915</v>
+        <v>72.9265345869151</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53480,11 +53480,11 @@
       </c>
       <c r="E101" s="19" t="n">
         <f aca="false">E94+E98+E99+E100</f>
-        <v>369.765991645786</v>
+        <v>369.765991645787</v>
       </c>
       <c r="F101" s="19" t="n">
         <f aca="false">F94+F98+F99+F100</f>
-        <v>483.865028099875</v>
+        <v>483.865028099876</v>
       </c>
       <c r="G101" s="19" t="n">
         <f aca="false">G94+G98+G99+G100</f>
@@ -53504,7 +53504,7 @@
       </c>
       <c r="E102" s="14" t="n">
         <f aca="false">E101/D101-1</f>
-        <v>0.641942348871955</v>
+        <v>0.641942348871957</v>
       </c>
       <c r="F102" s="14" t="n">
         <f aca="false">F101/E101-1</f>
@@ -53536,7 +53536,7 @@
       </c>
       <c r="F103" s="14" t="n">
         <f aca="false">F94/F101</f>
-        <v>0.611131441094207</v>
+        <v>0.611131441094208</v>
       </c>
       <c r="G103" s="14" t="n">
         <f aca="false">G94/G101</f>
@@ -53692,7 +53692,7 @@
       </c>
       <c r="F110" s="19" t="n">
         <f aca="false">E110*(1+MAX(0,phi*F102))</f>
-        <v>20.6288888178976</v>
+        <v>20.6288888178977</v>
       </c>
       <c r="G110" s="19" t="n">
         <f aca="false">F110*(1+MAX(0,phi*G102))</f>
@@ -53720,7 +53720,7 @@
       </c>
       <c r="F111" s="19" t="n">
         <f aca="false">F110+0*F101</f>
-        <v>20.6288888178976</v>
+        <v>20.6288888178977</v>
       </c>
       <c r="G111" s="19" t="n">
         <f aca="false">G110+0*G101</f>
@@ -53856,11 +53856,11 @@
       </c>
       <c r="E116" s="19" t="n">
         <f aca="false">(E112+E114)*E115</f>
-        <v>72.6551673339823</v>
+        <v>72.6551673339824</v>
       </c>
       <c r="F116" s="19" t="n">
         <f aca="false">(F112+F114)*F115</f>
-        <v>97.6307540794414</v>
+        <v>97.6307540794415</v>
       </c>
       <c r="G116" s="19" t="n">
         <f aca="false">(G112+G114)*G115</f>
@@ -53936,7 +53936,7 @@
       </c>
       <c r="E119" s="14" t="n">
         <f aca="false">E118/D118-1</f>
-        <v>0.74684138747603</v>
+        <v>0.746841387476032</v>
       </c>
       <c r="F119" s="14" t="n">
         <f aca="false">F118/E118-1</f>
@@ -53992,7 +53992,7 @@
       </c>
       <c r="D125" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E125" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -54115,7 +54115,7 @@
       </c>
       <c r="D130" s="20" t="n">
         <f aca="false">D127*D128*D129/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E130" s="20" t="n">
         <f aca="false">E127*E128*E129/1000</f>
@@ -54163,7 +54163,7 @@
       </c>
       <c r="D132" s="14" t="n">
         <f aca="false">a26_lc/D131</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H132" s="8" t="s">
         <v>468</v>
@@ -54202,7 +54202,7 @@
       </c>
       <c r="D134" s="14" t="n">
         <f aca="false">$D$132*D133</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E134" s="14" t="n">
         <f aca="false">$D$132*E133</f>
@@ -54214,7 +54214,7 @@
       </c>
       <c r="G134" s="14" t="n">
         <f aca="false">$D$132*G133</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54238,11 +54238,11 @@
       </c>
       <c r="F135" s="19" t="n">
         <f aca="false">F131*F134</f>
-        <v>181.043958316999</v>
+        <v>181.043958317</v>
       </c>
       <c r="G135" s="19" t="n">
         <f aca="false">G131*G134</f>
-        <v>194.780041714673</v>
+        <v>194.780041714674</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54259,7 +54259,7 @@
       </c>
       <c r="D137" s="22" t="n">
         <f aca="false">a26_air/D127</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54303,15 +54303,15 @@
       </c>
       <c r="E139" s="19" t="n">
         <f aca="false">E127*$D$137*E138</f>
-        <v>63.1282305747745</v>
+        <v>63.1282305747746</v>
       </c>
       <c r="F139" s="19" t="n">
         <f aca="false">F127*$D$137*F138</f>
-        <v>69.3527491354094</v>
+        <v>69.3527491354095</v>
       </c>
       <c r="G139" s="19" t="n">
         <f aca="false">G127*$D$137*G138</f>
-        <v>72.926534586915</v>
+        <v>72.9265345869151</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54411,7 +54411,7 @@
       </c>
       <c r="E143" s="14" t="n">
         <f aca="false">E142/D142-1</f>
-        <v>0.38028802753978</v>
+        <v>0.380288027539781</v>
       </c>
       <c r="F143" s="14" t="n">
         <f aca="false">F142/E142-1</f>
@@ -54443,7 +54443,7 @@
       </c>
       <c r="F144" s="14" t="n">
         <f aca="false">F135/F142</f>
-        <v>0.490363131670491</v>
+        <v>0.490363131670492</v>
       </c>
       <c r="G144" s="14" t="n">
         <f aca="false">G135/G142</f>
@@ -54467,7 +54467,7 @@
       </c>
       <c r="E145" s="14" t="n">
         <f aca="false">(E135+E139)/E142</f>
-        <v>0.637032278767946</v>
+        <v>0.637032278767947</v>
       </c>
       <c r="F145" s="14" t="n">
         <f aca="false">(F135+F139)/F142</f>
@@ -54475,7 +54475,7 @@
       </c>
       <c r="G145" s="14" t="n">
         <f aca="false">(G135+G139)/G142</f>
-        <v>0.683575483099721</v>
+        <v>0.683575483099722</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54499,7 +54499,7 @@
       </c>
       <c r="G146" s="18" t="n">
         <f aca="false">(G135+G139)/fx/G127*1000</f>
-        <v>139.109185431776</v>
+        <v>139.109185431777</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54547,7 +54547,7 @@
       </c>
       <c r="G149" s="19" t="n">
         <f aca="false">$D$148*G142+d_lc*G135</f>
-        <v>130.279861825436</v>
+        <v>130.279861825437</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54655,7 +54655,7 @@
       </c>
       <c r="F153" s="19" t="n">
         <f aca="false">F149-F152</f>
-        <v>105.896910709171</v>
+        <v>105.896910709172</v>
       </c>
       <c r="G153" s="19" t="n">
         <f aca="false">G149-G152</f>
@@ -54763,11 +54763,11 @@
       </c>
       <c r="E157" s="19" t="n">
         <f aca="false">(E153+E155)*E156</f>
-        <v>59.6713471560973</v>
+        <v>59.6713471560974</v>
       </c>
       <c r="F157" s="19" t="n">
         <f aca="false">(F153+F155)*F156</f>
-        <v>72.1554147286907</v>
+        <v>72.1554147286908</v>
       </c>
       <c r="G157" s="19" t="n">
         <f aca="false">(G153+G155)*G156</f>
@@ -54843,11 +54843,11 @@
       </c>
       <c r="E160" s="14" t="n">
         <f aca="false">E159/D159-1</f>
-        <v>0.434672614262461</v>
+        <v>0.434672614262462</v>
       </c>
       <c r="F160" s="14" t="n">
         <f aca="false">F159/E159-1</f>
-        <v>0.209213771224833</v>
+        <v>0.209213771224834</v>
       </c>
       <c r="G160" s="14" t="n">
         <f aca="false">G159/F159-1</f>
@@ -54899,7 +54899,7 @@
       </c>
       <c r="D166" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E166" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -55022,7 +55022,7 @@
       </c>
       <c r="D171" s="20" t="n">
         <f aca="false">D168*D169*D170/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E171" s="20" t="n">
         <f aca="false">E168*E169*E170/1000</f>
@@ -55070,7 +55070,7 @@
       </c>
       <c r="D173" s="14" t="n">
         <f aca="false">a26_lc/D172</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H173" s="8" t="s">
         <v>468</v>
@@ -55109,7 +55109,7 @@
       </c>
       <c r="D175" s="14" t="n">
         <f aca="false">$D$173*D174</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E175" s="14" t="n">
         <f aca="false">$D$173*E174</f>
@@ -55121,7 +55121,7 @@
       </c>
       <c r="G175" s="14" t="n">
         <f aca="false">$D$173*G174</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55149,7 +55149,7 @@
       </c>
       <c r="G176" s="19" t="n">
         <f aca="false">G172*G175</f>
-        <v>350.604075086412</v>
+        <v>350.604075086413</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55166,7 +55166,7 @@
       </c>
       <c r="D178" s="22" t="n">
         <f aca="false">a26_air/D168</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55210,15 +55210,15 @@
       </c>
       <c r="E180" s="19" t="n">
         <f aca="false">E168*$D$178*E179</f>
-        <v>63.1282305747745</v>
+        <v>63.1282305747746</v>
       </c>
       <c r="F180" s="19" t="n">
         <f aca="false">F168*$D$178*F179</f>
-        <v>69.3527491354094</v>
+        <v>69.3527491354095</v>
       </c>
       <c r="G180" s="19" t="n">
         <f aca="false">G168*$D$178*G179</f>
-        <v>72.926534586915</v>
+        <v>72.9265345869151</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55294,15 +55294,15 @@
       </c>
       <c r="E183" s="19" t="n">
         <f aca="false">E176+E180+E181+E182</f>
-        <v>391.773991489564</v>
+        <v>391.773991489565</v>
       </c>
       <c r="F183" s="19" t="n">
         <f aca="false">F176+F180+F181+F182</f>
-        <v>514.039021152708</v>
+        <v>514.039021152709</v>
       </c>
       <c r="G183" s="19" t="n">
         <f aca="false">G176+G180+G181+G182</f>
-        <v>547.450975706847</v>
+        <v>547.450975706848</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55318,7 +55318,7 @@
       </c>
       <c r="E184" s="14" t="n">
         <f aca="false">E183/D183-1</f>
-        <v>0.739668661658671</v>
+        <v>0.739668661658673</v>
       </c>
       <c r="F184" s="14" t="n">
         <f aca="false">F183/E183-1</f>
@@ -55374,7 +55374,7 @@
       </c>
       <c r="E186" s="14" t="n">
         <f aca="false">(E176+E180)/E183</f>
-        <v>0.712014125998955</v>
+        <v>0.712014125998956</v>
       </c>
       <c r="F186" s="14" t="n">
         <f aca="false">(F176+F180)/F183</f>
@@ -55406,7 +55406,7 @@
       </c>
       <c r="G187" s="18" t="n">
         <f aca="false">(G176+G180)/fx/G168*1000</f>
-        <v>220.080503553661</v>
+        <v>220.080503553662</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55506,7 +55506,7 @@
       </c>
       <c r="F192" s="19" t="n">
         <f aca="false">E192*(1+MAX(0,phi*F184))</f>
-        <v>21.6461971579801</v>
+        <v>21.6461971579802</v>
       </c>
       <c r="G192" s="19" t="n">
         <f aca="false">F192*(1+MAX(0,phi*G184))</f>
@@ -55534,7 +55534,7 @@
       </c>
       <c r="F193" s="19" t="n">
         <f aca="false">F192+0*F183</f>
-        <v>21.6461971579801</v>
+        <v>21.6461971579802</v>
       </c>
       <c r="G193" s="19" t="n">
         <f aca="false">G192+0*G183</f>
@@ -55750,7 +55750,7 @@
       </c>
       <c r="E201" s="14" t="n">
         <f aca="false">E200/D200-1</f>
-        <v>0.86343454373652</v>
+        <v>0.863434543736522</v>
       </c>
       <c r="F201" s="14" t="n">
         <f aca="false">F200/E200-1</f>
@@ -55758,7 +55758,7 @@
       </c>
       <c r="G201" s="14" t="n">
         <f aca="false">G200/F200-1</f>
-        <v>0.0686845139005661</v>
+        <v>0.0686845139005663</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55806,7 +55806,7 @@
       </c>
       <c r="D207" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E207" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -55953,7 +55953,7 @@
       </c>
       <c r="D213" s="19" t="n">
         <f aca="false">D212*fx</f>
-        <v>118.176547705101</v>
+        <v>118.1765477051</v>
       </c>
       <c r="E213" s="19" t="n">
         <f aca="false">E212*fx</f>
@@ -56020,15 +56020,15 @@
       </c>
       <c r="E216" s="14" t="n">
         <f aca="false">$D$214*E215</f>
-        <v>0.57931042774103</v>
+        <v>0.579310427741031</v>
       </c>
       <c r="F216" s="14" t="n">
         <f aca="false">$D$214*F215</f>
-        <v>0.548820405228344</v>
+        <v>0.548820405228345</v>
       </c>
       <c r="G216" s="14" t="n">
         <f aca="false">$D$214*G215</f>
-        <v>0.518330382715658</v>
+        <v>0.518330382715659</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56073,7 +56073,7 @@
       </c>
       <c r="D219" s="22" t="n">
         <f aca="false">a26_air/D209</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56117,15 +56117,15 @@
       </c>
       <c r="E221" s="19" t="n">
         <f aca="false">E209*$D$219*E220</f>
-        <v>63.1282305747745</v>
+        <v>63.1282305747746</v>
       </c>
       <c r="F221" s="19" t="n">
         <f aca="false">F209*$D$219*F220</f>
-        <v>69.3527491354094</v>
+        <v>69.3527491354095</v>
       </c>
       <c r="G221" s="19" t="n">
         <f aca="false">G209*$D$219*G220</f>
-        <v>72.926534586915</v>
+        <v>72.9265345869151</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56225,11 +56225,11 @@
       </c>
       <c r="E225" s="14" t="n">
         <f aca="false">E224/D224-1</f>
-        <v>0.453103711576941</v>
+        <v>0.453103711576942</v>
       </c>
       <c r="F225" s="14" t="n">
         <f aca="false">F224/E224-1</f>
-        <v>0.272534495514719</v>
+        <v>0.27253449551472</v>
       </c>
       <c r="G225" s="14" t="n">
         <f aca="false">G224/F224-1</f>
@@ -56261,7 +56261,7 @@
       </c>
       <c r="G226" s="14" t="n">
         <f aca="false">G217/G224</f>
-        <v>0.572044804784544</v>
+        <v>0.572044804784545</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56305,7 +56305,7 @@
       </c>
       <c r="E228" s="18" t="n">
         <f aca="false">(E217+E221)/fx/E209*1000</f>
-        <v>160.887409885349</v>
+        <v>160.88740988535</v>
       </c>
       <c r="F228" s="18" t="n">
         <f aca="false">(F217+F221)/fx/F209*1000</f>
@@ -56465,7 +56465,7 @@
       </c>
       <c r="E235" s="19" t="n">
         <f aca="false">E231-E234</f>
-        <v>92.7549772707592</v>
+        <v>92.7549772707593</v>
       </c>
       <c r="F235" s="19" t="n">
         <f aca="false">F231-F234</f>
@@ -56581,11 +56581,11 @@
       </c>
       <c r="F239" s="19" t="n">
         <f aca="false">(F235+F237)*F238</f>
-        <v>82.6465018118988</v>
+        <v>82.6465018118989</v>
       </c>
       <c r="G239" s="19" t="n">
         <f aca="false">(G235+G237)*G238</f>
-        <v>92.052487840432</v>
+        <v>92.0524878404321</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56633,7 +56633,7 @@
       </c>
       <c r="E241" s="20" t="n">
         <f aca="false">E239/E240</f>
-        <v>161.224990800019</v>
+        <v>161.22499080002</v>
       </c>
       <c r="F241" s="20" t="n">
         <f aca="false">F239/F240</f>
@@ -56657,11 +56657,11 @@
       </c>
       <c r="E242" s="14" t="n">
         <f aca="false">E241/D241-1</f>
-        <v>0.52154594637812</v>
+        <v>0.521545946378121</v>
       </c>
       <c r="F242" s="14" t="n">
         <f aca="false">F241/E241-1</f>
-        <v>0.305949460047928</v>
+        <v>0.305949460047929</v>
       </c>
       <c r="G242" s="14" t="n">
         <f aca="false">G241/F241-1</f>
@@ -56713,7 +56713,7 @@
       </c>
       <c r="D248" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E248" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -56836,7 +56836,7 @@
       </c>
       <c r="D253" s="20" t="n">
         <f aca="false">D250*D251*D252/1000</f>
-        <v>5.33435805613301</v>
+        <v>5.334358056133</v>
       </c>
       <c r="E253" s="20" t="n">
         <f aca="false">E250*E251*E252/1000</f>
@@ -56927,15 +56927,15 @@
       </c>
       <c r="E257" s="14" t="n">
         <f aca="false">$D$255*E256</f>
-        <v>0.401061065359174</v>
+        <v>0.401061065359175</v>
       </c>
       <c r="F257" s="14" t="n">
         <f aca="false">$D$255*F256</f>
-        <v>0.379952588235007</v>
+        <v>0.379952588235008</v>
       </c>
       <c r="G257" s="14" t="n">
         <f aca="false">$D$255*G256</f>
-        <v>0.35884411111084</v>
+        <v>0.358844111110841</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56980,7 +56980,7 @@
       </c>
       <c r="D260" s="22" t="n">
         <f aca="false">a26_air/D250</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57024,15 +57024,15 @@
       </c>
       <c r="E262" s="19" t="n">
         <f aca="false">E250*$D$260*E261</f>
-        <v>63.1282305747745</v>
+        <v>63.1282305747746</v>
       </c>
       <c r="F262" s="19" t="n">
         <f aca="false">F250*$D$260*F261</f>
-        <v>69.3527491354094</v>
+        <v>69.3527491354095</v>
       </c>
       <c r="G262" s="19" t="n">
         <f aca="false">G250*$D$260*G261</f>
-        <v>72.926534586915</v>
+        <v>72.9265345869151</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57108,11 +57108,11 @@
       </c>
       <c r="E265" s="19" t="n">
         <f aca="false">E258+E262+E263+E264</f>
-        <v>324.330121000567</v>
+        <v>324.330121000568</v>
       </c>
       <c r="F265" s="19" t="n">
         <f aca="false">F258+F262+F263+F264</f>
-        <v>402.627354496093</v>
+        <v>402.627354496094</v>
       </c>
       <c r="G265" s="19" t="n">
         <f aca="false">G258+G262+G263+G264</f>
@@ -57132,7 +57132,7 @@
       </c>
       <c r="E266" s="14" t="n">
         <f aca="false">E265/D265-1</f>
-        <v>0.440184799892929</v>
+        <v>0.44018479989293</v>
       </c>
       <c r="F266" s="14" t="n">
         <f aca="false">F265/E265-1</f>
@@ -57140,7 +57140,7 @@
       </c>
       <c r="G266" s="14" t="n">
         <f aca="false">G265/F265-1</f>
-        <v>0.0619902743240275</v>
+        <v>0.0619902743240277</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57220,7 +57220,7 @@
       </c>
       <c r="G269" s="18" t="n">
         <f aca="false">(G258+G262)/fx/G250*1000</f>
-        <v>157.794874229134</v>
+        <v>157.794874229135</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57372,7 +57372,7 @@
       </c>
       <c r="E276" s="19" t="n">
         <f aca="false">E272-E275</f>
-        <v>91.8052547494135</v>
+        <v>91.8052547494136</v>
       </c>
       <c r="F276" s="19" t="n">
         <f aca="false">F272-F275</f>
@@ -57484,15 +57484,15 @@
       </c>
       <c r="E280" s="19" t="n">
         <f aca="false">(E276+E278)*E279</f>
-        <v>62.6435469558541</v>
+        <v>62.6435469558542</v>
       </c>
       <c r="F280" s="19" t="n">
         <f aca="false">(F276+F278)*F279</f>
-        <v>79.5780008868546</v>
+        <v>79.5780008868547</v>
       </c>
       <c r="G280" s="19" t="n">
         <f aca="false">(G276+G278)*G279</f>
-        <v>84.8144771213928</v>
+        <v>84.8144771213929</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57564,7 +57564,7 @@
       </c>
       <c r="E283" s="14" t="n">
         <f aca="false">E282/D282-1</f>
-        <v>0.506132935841471</v>
+        <v>0.506132935841472</v>
       </c>
       <c r="F283" s="14" t="n">
         <f aca="false">F282/E282-1</f>
@@ -57572,7 +57572,7 @@
       </c>
       <c r="G283" s="14" t="n">
         <f aca="false">G282/F282-1</f>
-        <v>0.0658030633614881</v>
+        <v>0.0658030633614883</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57620,7 +57620,7 @@
       </c>
       <c r="D289" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E289" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -57743,7 +57743,7 @@
       </c>
       <c r="D294" s="20" t="n">
         <f aca="false">D291*D292*D293/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E294" s="20" t="n">
         <f aca="false">E291*E292*E293/1000</f>
@@ -57791,7 +57791,7 @@
       </c>
       <c r="D296" s="14" t="n">
         <f aca="false">a26_lc/D295</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H296" s="8" t="s">
         <v>468</v>
@@ -57830,7 +57830,7 @@
       </c>
       <c r="D298" s="14" t="n">
         <f aca="false">$D$296*D297</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E298" s="14" t="n">
         <f aca="false">$D$296*E297</f>
@@ -57842,7 +57842,7 @@
       </c>
       <c r="G298" s="14" t="n">
         <f aca="false">$D$296*G297</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57866,7 +57866,7 @@
       </c>
       <c r="F299" s="19" t="n">
         <f aca="false">F295*F298</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="G299" s="19" t="n">
         <f aca="false">G295*G298</f>
@@ -57887,7 +57887,7 @@
       </c>
       <c r="D301" s="22" t="n">
         <f aca="false">a26_air/D291</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57931,7 +57931,7 @@
       </c>
       <c r="E303" s="19" t="n">
         <f aca="false">E291*$D$301*E302</f>
-        <v>50.5025844598196</v>
+        <v>50.5025844598197</v>
       </c>
       <c r="F303" s="19" t="n">
         <f aca="false">F291*$D$301*F302</f>
@@ -57939,7 +57939,7 @@
       </c>
       <c r="G303" s="19" t="n">
         <f aca="false">G291*$D$301*G302</f>
-        <v>48.61768972461</v>
+        <v>48.6176897246101</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58015,7 +58015,7 @@
       </c>
       <c r="E306" s="19" t="n">
         <f aca="false">E299+E303+E304+E305</f>
-        <v>338.682023081211</v>
+        <v>338.682023081212</v>
       </c>
       <c r="F306" s="19" t="n">
         <f aca="false">F299+F303+F304+F305</f>
@@ -58039,7 +58039,7 @@
       </c>
       <c r="E307" s="14" t="n">
         <f aca="false">E306/D306-1</f>
-        <v>0.503914283797567</v>
+        <v>0.503914283797568</v>
       </c>
       <c r="F307" s="14" t="n">
         <f aca="false">F306/E306-1</f>
@@ -58047,7 +58047,7 @@
       </c>
       <c r="G307" s="14" t="n">
         <f aca="false">G306/F306-1</f>
-        <v>0.0593600868429074</v>
+        <v>0.0593600868429076</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58279,7 +58279,7 @@
       </c>
       <c r="E317" s="19" t="n">
         <f aca="false">E313-E316</f>
-        <v>97.247810924772</v>
+        <v>97.2478109247721</v>
       </c>
       <c r="F317" s="19" t="n">
         <f aca="false">F313-F316</f>
@@ -58287,7 +58287,7 @@
       </c>
       <c r="G317" s="19" t="n">
         <f aca="false">G313-G316</f>
-        <v>131.913857565624</v>
+        <v>131.913857565625</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58391,15 +58391,15 @@
       </c>
       <c r="E321" s="19" t="n">
         <f aca="false">(E317+E319)*E320</f>
-        <v>66.3172723742211</v>
+        <v>66.3172723742212</v>
       </c>
       <c r="F321" s="19" t="n">
         <f aca="false">(F317+F319)*F320</f>
-        <v>84.3575320178524</v>
+        <v>84.3575320178525</v>
       </c>
       <c r="G321" s="19" t="n">
         <f aca="false">(G317+G319)*G320</f>
-        <v>89.7168538567965</v>
+        <v>89.7168538567966</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58471,7 +58471,7 @@
       </c>
       <c r="E324" s="14" t="n">
         <f aca="false">E323/D323-1</f>
-        <v>0.594459972203888</v>
+        <v>0.594459972203889</v>
       </c>
       <c r="F324" s="14" t="n">
         <f aca="false">F323/E323-1</f>
@@ -58527,7 +58527,7 @@
       </c>
       <c r="D330" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E330" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -58650,7 +58650,7 @@
       </c>
       <c r="D335" s="20" t="n">
         <f aca="false">D332*D333*D334/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E335" s="20" t="n">
         <f aca="false">E332*E333*E334/1000</f>
@@ -58698,7 +58698,7 @@
       </c>
       <c r="D337" s="14" t="n">
         <f aca="false">a26_lc/D336</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H337" s="8" t="s">
         <v>468</v>
@@ -58737,7 +58737,7 @@
       </c>
       <c r="D339" s="14" t="n">
         <f aca="false">$D$337*D338</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E339" s="14" t="n">
         <f aca="false">$D$337*E338</f>
@@ -58749,7 +58749,7 @@
       </c>
       <c r="G339" s="14" t="n">
         <f aca="false">$D$337*G338</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58773,7 +58773,7 @@
       </c>
       <c r="F340" s="19" t="n">
         <f aca="false">F336*F339</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="G340" s="19" t="n">
         <f aca="false">G336*G339</f>
@@ -58794,7 +58794,7 @@
       </c>
       <c r="D342" s="22" t="n">
         <f aca="false">a26_air/D332</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58838,15 +58838,15 @@
       </c>
       <c r="E344" s="19" t="n">
         <f aca="false">E332*$D$342*E343</f>
-        <v>75.7538766897294</v>
+        <v>75.7538766897295</v>
       </c>
       <c r="F344" s="19" t="n">
         <f aca="false">F332*$D$342*F343</f>
-        <v>90.6920565616892</v>
+        <v>90.6920565616893</v>
       </c>
       <c r="G344" s="19" t="n">
         <f aca="false">G332*$D$342*G343</f>
-        <v>97.23537944922</v>
+        <v>97.2353794492202</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58926,7 +58926,7 @@
       </c>
       <c r="F347" s="19" t="n">
         <f aca="false">F340+F344+F345+F346</f>
-        <v>462.960745252188</v>
+        <v>462.960745252189</v>
       </c>
       <c r="G347" s="19" t="n">
         <f aca="false">G340+G344+G345+G346</f>
@@ -58946,7 +58946,7 @@
       </c>
       <c r="E348" s="14" t="n">
         <f aca="false">E347/D347-1</f>
-        <v>0.616042405400885</v>
+        <v>0.616042405400886</v>
       </c>
       <c r="F348" s="14" t="n">
         <f aca="false">F347/E347-1</f>
@@ -59030,7 +59030,7 @@
       </c>
       <c r="F351" s="18" t="n">
         <f aca="false">(F340+F344)/fx/F332*1000</f>
-        <v>203.719726315318</v>
+        <v>203.719726315319</v>
       </c>
       <c r="G351" s="18" t="n">
         <f aca="false">(G340+G344)/fx/G332*1000</f>
@@ -59134,7 +59134,7 @@
       </c>
       <c r="F356" s="19" t="n">
         <f aca="false">E356*(1+MAX(0,phi*F348))</f>
-        <v>19.9431995476837</v>
+        <v>19.9431995476838</v>
       </c>
       <c r="G356" s="19" t="n">
         <f aca="false">F356*(1+MAX(0,phi*G348))</f>
@@ -59162,7 +59162,7 @@
       </c>
       <c r="F357" s="19" t="n">
         <f aca="false">F356+0*F347</f>
-        <v>19.9431995476837</v>
+        <v>19.9431995476838</v>
       </c>
       <c r="G357" s="19" t="n">
         <f aca="false">G356+0*G347</f>
@@ -59302,11 +59302,11 @@
       </c>
       <c r="F362" s="19" t="n">
         <f aca="false">(F358+F360)*F361</f>
-        <v>92.1097991427082</v>
+        <v>92.1097991427083</v>
       </c>
       <c r="G362" s="19" t="n">
         <f aca="false">(G358+G360)*G361</f>
-        <v>98.5734101847196</v>
+        <v>98.5734101847197</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59354,15 +59354,15 @@
       </c>
       <c r="E364" s="20" t="n">
         <f aca="false">E362/E363</f>
-        <v>180.520675376328</v>
+        <v>180.520675376329</v>
       </c>
       <c r="F364" s="20" t="n">
         <f aca="false">F362/F363</f>
-        <v>234.660553327016</v>
+        <v>234.660553327017</v>
       </c>
       <c r="G364" s="20" t="n">
         <f aca="false">G362/G363</f>
-        <v>251.127363131465</v>
+        <v>251.127363131466</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59378,15 +59378,15 @@
       </c>
       <c r="E365" s="14" t="n">
         <f aca="false">E364/D364-1</f>
-        <v>0.703647185795093</v>
+        <v>0.703647185795095</v>
       </c>
       <c r="F365" s="14" t="n">
         <f aca="false">F364/E364-1</f>
-        <v>0.299909569016531</v>
+        <v>0.299909569016532</v>
       </c>
       <c r="G365" s="14" t="n">
         <f aca="false">G364/F364-1</f>
-        <v>0.0701728925930794</v>
+        <v>0.0701728925930789</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59434,7 +59434,7 @@
       </c>
       <c r="D371" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E371" s="20" t="n">
         <f aca="false">itc_27*1*mf_lo</f>
@@ -59557,7 +59557,7 @@
       </c>
       <c r="D376" s="20" t="n">
         <f aca="false">D373*D374*D375/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E376" s="20" t="n">
         <f aca="false">E373*E374*E375/1000</f>
@@ -59605,7 +59605,7 @@
       </c>
       <c r="D378" s="14" t="n">
         <f aca="false">a26_lc/D377</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H378" s="8" t="s">
         <v>468</v>
@@ -59644,7 +59644,7 @@
       </c>
       <c r="D380" s="14" t="n">
         <f aca="false">$D$378*D379</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E380" s="14" t="n">
         <f aca="false">$D$378*E379</f>
@@ -59656,7 +59656,7 @@
       </c>
       <c r="G380" s="14" t="n">
         <f aca="false">$D$378*G379</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59676,15 +59676,15 @@
       </c>
       <c r="E381" s="19" t="n">
         <f aca="false">E377*E380</f>
-        <v>140.283250617113</v>
+        <v>140.283250617114</v>
       </c>
       <c r="F381" s="19" t="n">
         <f aca="false">F377*F380</f>
-        <v>202.769233315039</v>
+        <v>202.76923331504</v>
       </c>
       <c r="G381" s="19" t="n">
         <f aca="false">G377*G380</f>
-        <v>218.153646720434</v>
+        <v>218.153646720435</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59701,7 +59701,7 @@
       </c>
       <c r="D383" s="22" t="n">
         <f aca="false">a26_air/D373</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59745,15 +59745,15 @@
       </c>
       <c r="E385" s="19" t="n">
         <f aca="false">E373*$D$383*E384</f>
-        <v>50.5025844598196</v>
+        <v>50.5025844598197</v>
       </c>
       <c r="F385" s="19" t="n">
         <f aca="false">F373*$D$383*F384</f>
-        <v>55.4821993083275</v>
+        <v>55.4821993083276</v>
       </c>
       <c r="G385" s="19" t="n">
         <f aca="false">G373*$D$383*G384</f>
-        <v>58.341227669532</v>
+        <v>58.3412276695321</v>
       </c>
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59837,7 +59837,7 @@
       </c>
       <c r="G388" s="19" t="n">
         <f aca="false">G381+G385+G386+G387</f>
-        <v>400.415240423486</v>
+        <v>400.415240423487</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59853,7 +59853,7 @@
       </c>
       <c r="E389" s="14" t="n">
         <f aca="false">E388/D388-1</f>
-        <v>0.34818267567938</v>
+        <v>0.348182675679382</v>
       </c>
       <c r="F389" s="14" t="n">
         <f aca="false">F388/E388-1</f>
@@ -59861,7 +59861,7 @@
       </c>
       <c r="G389" s="14" t="n">
         <f aca="false">G388/F388-1</f>
-        <v>0.0619443821537145</v>
+        <v>0.0619443821537147</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59885,11 +59885,11 @@
       </c>
       <c r="F390" s="14" t="n">
         <f aca="false">F381/F388</f>
-        <v>0.537765865167333</v>
+        <v>0.537765865167334</v>
       </c>
       <c r="G390" s="14" t="n">
         <f aca="false">G381/G388</f>
-        <v>0.544818540097802</v>
+        <v>0.544818540097803</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59913,7 +59913,7 @@
       </c>
       <c r="F391" s="14" t="n">
         <f aca="false">(F381+F385)/F388</f>
-        <v>0.684910638684688</v>
+        <v>0.684910638684689</v>
       </c>
       <c r="G391" s="14" t="n">
         <f aca="false">(G381+G385)/G388</f>
@@ -59933,7 +59933,7 @@
       </c>
       <c r="E392" s="18" t="n">
         <f aca="false">(E381+E385)/fx/E373*1000</f>
-        <v>178.947189172338</v>
+        <v>178.947189172339</v>
       </c>
       <c r="F392" s="18" t="n">
         <f aca="false">(F381+F385)/fx/F373*1000</f>
@@ -60093,7 +60093,7 @@
       </c>
       <c r="E399" s="19" t="n">
         <f aca="false">E395-E398</f>
-        <v>85.7993376220051</v>
+        <v>85.7993376220052</v>
       </c>
       <c r="F399" s="19" t="n">
         <f aca="false">F395-F398</f>
@@ -60209,11 +60209,11 @@
       </c>
       <c r="F403" s="19" t="n">
         <f aca="false">(F399+F401)*F402</f>
-        <v>74.4692147234936</v>
+        <v>74.4692147234937</v>
       </c>
       <c r="G403" s="19" t="n">
         <f aca="false">(G399+G401)*G402</f>
-        <v>79.368253701954</v>
+        <v>79.3682537019541</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60285,7 +60285,7 @@
       </c>
       <c r="E406" s="14" t="n">
         <f aca="false">E405/D405-1</f>
-        <v>0.408663136098462</v>
+        <v>0.408663136098463</v>
       </c>
       <c r="F406" s="14" t="n">
         <f aca="false">F405/E405-1</f>
@@ -60293,7 +60293,7 @@
       </c>
       <c r="G406" s="14" t="n">
         <f aca="false">G405/F405-1</f>
-        <v>0.065786096934829</v>
+        <v>0.0657860969348294</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60341,7 +60341,7 @@
       </c>
       <c r="D412" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E412" s="20" t="n">
         <f aca="false">itc_27*1*mf_hi</f>
@@ -60464,7 +60464,7 @@
       </c>
       <c r="D417" s="20" t="n">
         <f aca="false">D414*D415*D416/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E417" s="20" t="n">
         <f aca="false">E414*E415*E416/1000</f>
@@ -60512,7 +60512,7 @@
       </c>
       <c r="D419" s="14" t="n">
         <f aca="false">a26_lc/D418</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H419" s="8" t="s">
         <v>468</v>
@@ -60551,7 +60551,7 @@
       </c>
       <c r="D421" s="14" t="n">
         <f aca="false">$D$419*D420</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E421" s="14" t="n">
         <f aca="false">$D$419*E420</f>
@@ -60563,7 +60563,7 @@
       </c>
       <c r="G421" s="14" t="n">
         <f aca="false">$D$419*G420</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60587,11 +60587,11 @@
       </c>
       <c r="F422" s="19" t="n">
         <f aca="false">F418*F421</f>
-        <v>304.153849972559</v>
+        <v>304.15384997256</v>
       </c>
       <c r="G422" s="19" t="n">
         <f aca="false">G418*G421</f>
-        <v>327.230470080651</v>
+        <v>327.230470080652</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60608,7 +60608,7 @@
       </c>
       <c r="D424" s="22" t="n">
         <f aca="false">a26_air/D414</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60652,7 +60652,7 @@
       </c>
       <c r="E426" s="19" t="n">
         <f aca="false">E414*$D$424*E425</f>
-        <v>75.7538766897294</v>
+        <v>75.7538766897295</v>
       </c>
       <c r="F426" s="19" t="n">
         <f aca="false">F414*$D$424*F425</f>
@@ -60660,7 +60660,7 @@
       </c>
       <c r="G426" s="19" t="n">
         <f aca="false">G414*$D$424*G425</f>
-        <v>87.511841504298</v>
+        <v>87.5118415042981</v>
       </c>
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60736,15 +60736,15 @@
       </c>
       <c r="E429" s="19" t="n">
         <f aca="false">E422+E426+E427+E428</f>
-        <v>399.004127965399</v>
+        <v>399.0041279654</v>
       </c>
       <c r="F429" s="19" t="n">
         <f aca="false">F422+F426+F427+F428</f>
-        <v>506.18429598175</v>
+        <v>506.184295981751</v>
       </c>
       <c r="G429" s="19" t="n">
         <f aca="false">G422+G426+G427+G428</f>
-        <v>538.662677618469</v>
+        <v>538.66267761847</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60760,7 +60760,7 @@
       </c>
       <c r="E430" s="14" t="n">
         <f aca="false">E429/D429-1</f>
-        <v>0.771774013519071</v>
+        <v>0.771774013519073</v>
       </c>
       <c r="F430" s="14" t="n">
         <f aca="false">F429/E429-1</f>
@@ -60768,7 +60768,7 @@
       </c>
       <c r="G430" s="14" t="n">
         <f aca="false">G429/F429-1</f>
-        <v>0.0641631553853856</v>
+        <v>0.0641631553853859</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60788,7 +60788,7 @@
       </c>
       <c r="E431" s="14" t="n">
         <f aca="false">E422/E429</f>
-        <v>0.527375185311159</v>
+        <v>0.52737518531116</v>
       </c>
       <c r="F431" s="14" t="n">
         <f aca="false">F422/F429</f>
@@ -60840,7 +60840,7 @@
       </c>
       <c r="E433" s="18" t="n">
         <f aca="false">(E422+E426)/fx/E414*1000</f>
-        <v>178.947189172338</v>
+        <v>178.947189172339</v>
       </c>
       <c r="F433" s="18" t="n">
         <f aca="false">(F422+F426)/fx/F414*1000</f>
@@ -61112,7 +61112,7 @@
       </c>
       <c r="E444" s="19" t="n">
         <f aca="false">(E440+E442)*E443</f>
-        <v>78.586340215882</v>
+        <v>78.5863402158821</v>
       </c>
       <c r="F444" s="19" t="n">
         <f aca="false">(F440+F442)*F443</f>
@@ -61120,7 +61120,7 @@
       </c>
       <c r="G444" s="19" t="n">
         <f aca="false">(G440+G442)*G443</f>
-        <v>108.926266059287</v>
+        <v>108.926266059288</v>
       </c>
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61192,7 +61192,7 @@
       </c>
       <c r="E447" s="14" t="n">
         <f aca="false">E446/D446-1</f>
-        <v>0.889444021900518</v>
+        <v>0.88944402190052</v>
       </c>
       <c r="F447" s="14" t="n">
         <f aca="false">F446/E446-1</f>
@@ -61200,7 +61200,7 @@
       </c>
       <c r="G447" s="14" t="n">
         <f aca="false">G446/F446-1</f>
-        <v>0.0678807632322478</v>
+        <v>0.067880763232248</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61248,7 +61248,7 @@
       </c>
       <c r="D453" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E453" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -61371,7 +61371,7 @@
       </c>
       <c r="D458" s="20" t="n">
         <f aca="false">D455*D456*D457/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E458" s="20" t="n">
         <f aca="false">E455*E456*E457/1000</f>
@@ -61419,7 +61419,7 @@
       </c>
       <c r="D460" s="14" t="n">
         <f aca="false">a26_lc/D459</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H460" s="8" t="s">
         <v>468</v>
@@ -61458,7 +61458,7 @@
       </c>
       <c r="D462" s="14" t="n">
         <f aca="false">$D$460*D461</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E462" s="14" t="n">
         <f aca="false">$D$460*E461</f>
@@ -61470,7 +61470,7 @@
       </c>
       <c r="G462" s="14" t="n">
         <f aca="false">$D$460*G461</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61494,7 +61494,7 @@
       </c>
       <c r="F463" s="19" t="n">
         <f aca="false">F459*F462</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="G463" s="19" t="n">
         <f aca="false">G459*G462</f>
@@ -61515,7 +61515,7 @@
       </c>
       <c r="D465" s="22" t="n">
         <f aca="false">a26_air/D455</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="466" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61559,15 +61559,15 @@
       </c>
       <c r="E467" s="19" t="n">
         <f aca="false">E455*$D$465*E466</f>
-        <v>63.1282305747745</v>
+        <v>63.1282305747746</v>
       </c>
       <c r="F467" s="19" t="n">
         <f aca="false">F455*$D$465*F466</f>
-        <v>69.3527491354094</v>
+        <v>69.3527491354095</v>
       </c>
       <c r="G467" s="19" t="n">
         <f aca="false">G455*$D$465*G466</f>
-        <v>72.926534586915</v>
+        <v>72.9265345869151</v>
       </c>
     </row>
     <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61643,7 +61643,7 @@
       </c>
       <c r="E470" s="19" t="n">
         <f aca="false">E463+E467+E468+E469</f>
-        <v>344.326458346166</v>
+        <v>344.326458346167</v>
       </c>
       <c r="F470" s="19" t="n">
         <f aca="false">F463+F467+F468+F469</f>
@@ -61667,7 +61667,7 @@
       </c>
       <c r="E471" s="14" t="n">
         <f aca="false">E470/D470-1</f>
-        <v>0.528978344599226</v>
+        <v>0.528978344599227</v>
       </c>
       <c r="F471" s="14" t="n">
         <f aca="false">F470/E470-1</f>
@@ -61675,7 +61675,7 @@
       </c>
       <c r="G471" s="14" t="n">
         <f aca="false">G470/F470-1</f>
-        <v>0.0531992357257844</v>
+        <v>0.0531992357257847</v>
       </c>
     </row>
     <row r="472" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61747,7 +61747,7 @@
       </c>
       <c r="E474" s="18" t="n">
         <f aca="false">(E463+E467)/fx/E455*1000</f>
-        <v>178.947189172338</v>
+        <v>178.947189172339</v>
       </c>
       <c r="F474" s="18" t="n">
         <f aca="false">(F463+F467)/fx/F455*1000</f>
@@ -61855,7 +61855,7 @@
       </c>
       <c r="F479" s="19" t="n">
         <f aca="false">E479*(1+MAX(0,phi*F471))</f>
-        <v>18.7887667271083</v>
+        <v>18.7887667271084</v>
       </c>
       <c r="G479" s="19" t="n">
         <f aca="false">F479*(1+MAX(0,phi*G471))</f>
@@ -61883,7 +61883,7 @@
       </c>
       <c r="F480" s="19" t="n">
         <f aca="false">F479+0*F470</f>
-        <v>18.7887667271083</v>
+        <v>18.7887667271084</v>
       </c>
       <c r="G480" s="19" t="n">
         <f aca="false">G479+0*G470</f>
@@ -61907,7 +61907,7 @@
       </c>
       <c r="E481" s="19" t="n">
         <f aca="false">E477-E480</f>
-        <v>98.7517073715689</v>
+        <v>98.751707371569</v>
       </c>
       <c r="F481" s="19" t="n">
         <f aca="false">F477-F480</f>
@@ -62019,15 +62019,15 @@
       </c>
       <c r="E485" s="19" t="n">
         <f aca="false">(E481+E483)*E484</f>
-        <v>67.332402475809</v>
+        <v>67.3324024758091</v>
       </c>
       <c r="F485" s="19" t="n">
         <f aca="false">(F481+F483)*F484</f>
-        <v>85.877498365839</v>
+        <v>85.8774983658391</v>
       </c>
       <c r="G485" s="19" t="n">
         <f aca="false">(G481+G483)*G484</f>
-        <v>90.845350173371</v>
+        <v>90.8453501733712</v>
       </c>
     </row>
     <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62099,7 +62099,7 @@
       </c>
       <c r="E488" s="14" t="n">
         <f aca="false">E487/D487-1</f>
-        <v>0.618866650217236</v>
+        <v>0.618866650217237</v>
       </c>
       <c r="F488" s="14" t="n">
         <f aca="false">F487/E487-1</f>
@@ -62107,7 +62107,7 @@
       </c>
       <c r="G488" s="14" t="n">
         <f aca="false">G487/F487-1</f>
-        <v>0.0578481197294423</v>
+        <v>0.0578481197294425</v>
       </c>
     </row>
     <row r="491" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62155,7 +62155,7 @@
       </c>
       <c r="D494" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E494" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -62278,7 +62278,7 @@
       </c>
       <c r="D499" s="20" t="n">
         <f aca="false">D496*D497*D498/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E499" s="20" t="n">
         <f aca="false">E496*E497*E498/1000</f>
@@ -62326,7 +62326,7 @@
       </c>
       <c r="D501" s="14" t="n">
         <f aca="false">a26_lc/D500</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H501" s="8" t="s">
         <v>468</v>
@@ -62365,7 +62365,7 @@
       </c>
       <c r="D503" s="14" t="n">
         <f aca="false">$D$501*D502</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E503" s="14" t="n">
         <f aca="false">$D$501*E502</f>
@@ -62377,7 +62377,7 @@
       </c>
       <c r="G503" s="14" t="n">
         <f aca="false">$D$501*G502</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62401,7 +62401,7 @@
       </c>
       <c r="F504" s="19" t="n">
         <f aca="false">F500*F503</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="G504" s="19" t="n">
         <f aca="false">G500*G503</f>
@@ -62422,7 +62422,7 @@
       </c>
       <c r="D506" s="22" t="n">
         <f aca="false">a26_air/D496</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="507" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62466,15 +62466,15 @@
       </c>
       <c r="E508" s="19" t="n">
         <f aca="false">E496*$D$506*E507</f>
-        <v>63.1282305747745</v>
+        <v>63.1282305747746</v>
       </c>
       <c r="F508" s="19" t="n">
         <f aca="false">F496*$D$506*F507</f>
-        <v>69.3527491354094</v>
+        <v>69.3527491354095</v>
       </c>
       <c r="G508" s="19" t="n">
         <f aca="false">G496*$D$506*G507</f>
-        <v>72.926534586915</v>
+        <v>72.9265345869151</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62574,7 +62574,7 @@
       </c>
       <c r="E512" s="14" t="n">
         <f aca="false">E511/D511-1</f>
-        <v>0.589578344599225</v>
+        <v>0.589578344599227</v>
       </c>
       <c r="F512" s="14" t="n">
         <f aca="false">F511/E511-1</f>
@@ -62630,7 +62630,7 @@
       </c>
       <c r="E514" s="14" t="n">
         <f aca="false">(E504+E508)/E511</f>
-        <v>0.666200787269923</v>
+        <v>0.666200787269924</v>
       </c>
       <c r="F514" s="14" t="n">
         <f aca="false">(F504+F508)/F511</f>
@@ -62638,7 +62638,7 @@
       </c>
       <c r="G514" s="14" t="n">
         <f aca="false">(G504+G508)/G511</f>
-        <v>0.706541462675686</v>
+        <v>0.706541462675687</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62654,7 +62654,7 @@
       </c>
       <c r="E515" s="18" t="n">
         <f aca="false">(E504+E508)/fx/E496*1000</f>
-        <v>178.947189172338</v>
+        <v>178.947189172339</v>
       </c>
       <c r="F515" s="18" t="n">
         <f aca="false">(F504+F508)/fx/F496*1000</f>
@@ -62706,7 +62706,7 @@
       </c>
       <c r="F518" s="19" t="n">
         <f aca="false">$D$517*F511+d_lc*F504</f>
-        <v>152.985381263197</v>
+        <v>152.985381263198</v>
       </c>
       <c r="G518" s="19" t="n">
         <f aca="false">$D$517*G511+d_lc*G504</f>
@@ -62926,15 +62926,15 @@
       </c>
       <c r="E526" s="19" t="n">
         <f aca="false">(E522+E524)*E525</f>
-        <v>69.7867886442367</v>
+        <v>69.7867886442368</v>
       </c>
       <c r="F526" s="19" t="n">
         <f aca="false">(F522+F524)*F525</f>
-        <v>90.6614303875557</v>
+        <v>90.6614303875558</v>
       </c>
       <c r="G526" s="19" t="n">
         <f aca="false">(G522+G524)*G525</f>
-        <v>97.7303129267636</v>
+        <v>97.7303129267637</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63006,15 +63006,15 @@
       </c>
       <c r="E529" s="14" t="n">
         <f aca="false">E528/D528-1</f>
-        <v>0.677877227127062</v>
+        <v>0.677877227127063</v>
       </c>
       <c r="F529" s="14" t="n">
         <f aca="false">F528/E528-1</f>
-        <v>0.299120251108486</v>
+        <v>0.299120251108487</v>
       </c>
       <c r="G529" s="14" t="n">
         <f aca="false">G528/F528-1</f>
-        <v>0.0779701192556763</v>
+        <v>0.0779701192556768</v>
       </c>
     </row>
     <row r="532" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63062,7 +63062,7 @@
       </c>
       <c r="D535" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E535" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -63185,7 +63185,7 @@
       </c>
       <c r="D540" s="20" t="n">
         <f aca="false">D537*D538*D539/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E540" s="20" t="n">
         <f aca="false">E537*E538*E539/1000</f>
@@ -63233,7 +63233,7 @@
       </c>
       <c r="D542" s="14" t="n">
         <f aca="false">a26_lc/D541</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H542" s="8" t="s">
         <v>468</v>
@@ -63272,7 +63272,7 @@
       </c>
       <c r="D544" s="14" t="n">
         <f aca="false">$D$542*D543</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E544" s="14" t="n">
         <f aca="false">$D$542*E543</f>
@@ -63284,7 +63284,7 @@
       </c>
       <c r="G544" s="14" t="n">
         <f aca="false">$D$542*G543</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
     </row>
     <row r="545" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63308,7 +63308,7 @@
       </c>
       <c r="F545" s="19" t="n">
         <f aca="false">F541*F544</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="G545" s="19" t="n">
         <f aca="false">G541*G544</f>
@@ -63329,7 +63329,7 @@
       </c>
       <c r="D547" s="22" t="n">
         <f aca="false">a26_air/D537</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="548" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63373,15 +63373,15 @@
       </c>
       <c r="E549" s="19" t="n">
         <f aca="false">E537*$D$547*E548</f>
-        <v>63.1282305747745</v>
+        <v>63.1282305747746</v>
       </c>
       <c r="F549" s="19" t="n">
         <f aca="false">F537*$D$547*F548</f>
-        <v>69.3527491354094</v>
+        <v>69.3527491354095</v>
       </c>
       <c r="G549" s="19" t="n">
         <f aca="false">G537*$D$547*G548</f>
-        <v>72.926534586915</v>
+        <v>72.9265345869151</v>
       </c>
     </row>
     <row r="550" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63457,7 +63457,7 @@
       </c>
       <c r="E552" s="19" t="n">
         <f aca="false">E545+E549+E550+E551</f>
-        <v>351.307669196166</v>
+        <v>351.307669196167</v>
       </c>
       <c r="F552" s="19" t="n">
         <f aca="false">F545+F549+F550+F551</f>
@@ -63481,7 +63481,7 @@
       </c>
       <c r="E553" s="14" t="n">
         <f aca="false">E552/D552-1</f>
-        <v>0.559978344599226</v>
+        <v>0.559978344599227</v>
       </c>
       <c r="F553" s="14" t="n">
         <f aca="false">F552/E552-1</f>
@@ -63545,7 +63545,7 @@
       </c>
       <c r="G555" s="14" t="n">
         <f aca="false">(G545+G549)/G552</f>
-        <v>0.7360807582572</v>
+        <v>0.736080758257201</v>
       </c>
     </row>
     <row r="556" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63561,7 +63561,7 @@
       </c>
       <c r="E556" s="18" t="n">
         <f aca="false">(E545+E549)/fx/E537*1000</f>
-        <v>178.947189172338</v>
+        <v>178.947189172339</v>
       </c>
       <c r="F556" s="18" t="n">
         <f aca="false">(F545+F549)/fx/F537*1000</f>
@@ -63613,7 +63613,7 @@
       </c>
       <c r="F559" s="19" t="n">
         <f aca="false">$D$558*F552+d_lc_lo*F545</f>
-        <v>144.4544528296</v>
+        <v>144.454452829601</v>
       </c>
       <c r="G559" s="19" t="n">
         <f aca="false">$D$558*G552+d_lc_lo*G545</f>
@@ -63669,7 +63669,7 @@
       </c>
       <c r="F561" s="19" t="n">
         <f aca="false">E561*(1+MAX(0,phi*F553))</f>
-        <v>19.2249952047764</v>
+        <v>19.2249952047765</v>
       </c>
       <c r="G561" s="19" t="n">
         <f aca="false">F561*(1+MAX(0,phi*G553))</f>
@@ -63697,7 +63697,7 @@
       </c>
       <c r="F562" s="19" t="n">
         <f aca="false">F561+0*F552</f>
-        <v>19.2249952047764</v>
+        <v>19.2249952047765</v>
       </c>
       <c r="G562" s="19" t="n">
         <f aca="false">G561+0*G552</f>
@@ -63721,7 +63721,7 @@
       </c>
       <c r="E563" s="19" t="n">
         <f aca="false">E559-E562</f>
-        <v>98.0943483094741</v>
+        <v>98.0943483094742</v>
       </c>
       <c r="F563" s="19" t="n">
         <f aca="false">F559-F562</f>
@@ -63837,7 +63837,7 @@
       </c>
       <c r="F567" s="19" t="n">
         <f aca="false">(F563+F565)*F566</f>
-        <v>85.2048838967562</v>
+        <v>85.2048838967563</v>
       </c>
       <c r="G567" s="19" t="n">
         <f aca="false">(G563+G565)*G566</f>
@@ -63913,7 +63913,7 @@
       </c>
       <c r="E570" s="14" t="n">
         <f aca="false">E569/D569-1</f>
-        <v>0.608198395097759</v>
+        <v>0.608198395097761</v>
       </c>
       <c r="F570" s="14" t="n">
         <f aca="false">F569/E569-1</f>
@@ -63921,7 +63921,7 @@
       </c>
       <c r="G570" s="14" t="n">
         <f aca="false">G569/F569-1</f>
-        <v>0.0661117617385385</v>
+        <v>0.0661117617385383</v>
       </c>
     </row>
     <row r="573" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63969,7 +63969,7 @@
       </c>
       <c r="D576" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E576" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -64092,7 +64092,7 @@
       </c>
       <c r="D581" s="20" t="n">
         <f aca="false">D578*D579*D580/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E581" s="20" t="n">
         <f aca="false">E578*E579*E580/1000</f>
@@ -64140,7 +64140,7 @@
       </c>
       <c r="D583" s="14" t="n">
         <f aca="false">a26_lc/D582</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H583" s="8" t="s">
         <v>468</v>
@@ -64179,7 +64179,7 @@
       </c>
       <c r="D585" s="14" t="n">
         <f aca="false">$D$583*D584</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E585" s="14" t="n">
         <f aca="false">$D$583*E584</f>
@@ -64191,7 +64191,7 @@
       </c>
       <c r="G585" s="14" t="n">
         <f aca="false">$D$583*G584</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
     </row>
     <row r="586" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64215,7 +64215,7 @@
       </c>
       <c r="F586" s="19" t="n">
         <f aca="false">F582*F585</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="G586" s="19" t="n">
         <f aca="false">G582*G585</f>
@@ -64236,7 +64236,7 @@
       </c>
       <c r="D588" s="22" t="n">
         <f aca="false">a26_air/D578</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="589" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64280,15 +64280,15 @@
       </c>
       <c r="E590" s="19" t="n">
         <f aca="false">E578*$D$588*E589</f>
-        <v>63.1282305747745</v>
+        <v>63.1282305747746</v>
       </c>
       <c r="F590" s="19" t="n">
         <f aca="false">F578*$D$588*F589</f>
-        <v>69.3527491354094</v>
+        <v>69.3527491354095</v>
       </c>
       <c r="G590" s="19" t="n">
         <f aca="false">G578*$D$588*G589</f>
-        <v>72.926534586915</v>
+        <v>72.9265345869151</v>
       </c>
     </row>
     <row r="591" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64364,7 +64364,7 @@
       </c>
       <c r="E593" s="19" t="n">
         <f aca="false">E586+E590+E591+E592</f>
-        <v>351.307669196166</v>
+        <v>351.307669196167</v>
       </c>
       <c r="F593" s="19" t="n">
         <f aca="false">F586+F590+F591+F592</f>
@@ -64388,7 +64388,7 @@
       </c>
       <c r="E594" s="14" t="n">
         <f aca="false">E593/D593-1</f>
-        <v>0.559978344599226</v>
+        <v>0.559978344599227</v>
       </c>
       <c r="F594" s="14" t="n">
         <f aca="false">F593/E593-1</f>
@@ -64452,7 +64452,7 @@
       </c>
       <c r="G596" s="14" t="n">
         <f aca="false">(G586+G590)/G593</f>
-        <v>0.7360807582572</v>
+        <v>0.736080758257201</v>
       </c>
     </row>
     <row r="597" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64468,7 +64468,7 @@
       </c>
       <c r="E597" s="18" t="n">
         <f aca="false">(E586+E590)/fx/E578*1000</f>
-        <v>178.947189172338</v>
+        <v>178.947189172339</v>
       </c>
       <c r="F597" s="18" t="n">
         <f aca="false">(F586+F590)/fx/F578*1000</f>
@@ -64576,7 +64576,7 @@
       </c>
       <c r="F602" s="19" t="n">
         <f aca="false">E602*(1+MAX(0,phi*F594))</f>
-        <v>19.2249952047764</v>
+        <v>19.2249952047765</v>
       </c>
       <c r="G602" s="19" t="n">
         <f aca="false">F602*(1+MAX(0,phi*G594))</f>
@@ -64604,7 +64604,7 @@
       </c>
       <c r="F603" s="19" t="n">
         <f aca="false">F602+0*F593</f>
-        <v>19.2249952047764</v>
+        <v>19.2249952047765</v>
       </c>
       <c r="G603" s="19" t="n">
         <f aca="false">G602+0*G593</f>
@@ -64740,7 +64740,7 @@
       </c>
       <c r="E608" s="19" t="n">
         <f aca="false">(E604+E606)*E607</f>
-        <v>70.2872080018404</v>
+        <v>70.2872080018405</v>
       </c>
       <c r="F608" s="19" t="n">
         <f aca="false">(F604+F606)*F607</f>
@@ -64748,7 +64748,7 @@
       </c>
       <c r="G608" s="19" t="n">
         <f aca="false">(G604+G606)*G607</f>
-        <v>97.4496668216452</v>
+        <v>97.4496668216453</v>
       </c>
     </row>
     <row r="609" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64800,7 +64800,7 @@
       </c>
       <c r="F610" s="20" t="n">
         <f aca="false">F608/F609</f>
-        <v>232.497089783966</v>
+        <v>232.497089783967</v>
       </c>
       <c r="G610" s="20" t="n">
         <f aca="false">G608/G609</f>
@@ -64820,11 +64820,11 @@
       </c>
       <c r="E611" s="14" t="n">
         <f aca="false">E610/D610-1</f>
-        <v>0.689908762901221</v>
+        <v>0.689908762901223</v>
       </c>
       <c r="F611" s="14" t="n">
         <f aca="false">F610/E610-1</f>
-        <v>0.298395416382168</v>
+        <v>0.298395416382167</v>
       </c>
       <c r="G611" s="14" t="n">
         <f aca="false">G610/F610-1</f>
@@ -64876,7 +64876,7 @@
       </c>
       <c r="D617" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E617" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -64999,7 +64999,7 @@
       </c>
       <c r="D622" s="20" t="n">
         <f aca="false">D619*D620*D621/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E622" s="20" t="n">
         <f aca="false">E619*E620*E621/1000</f>
@@ -65047,7 +65047,7 @@
       </c>
       <c r="D624" s="14" t="n">
         <f aca="false">a26_lc/D623</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H624" s="8" t="s">
         <v>468</v>
@@ -65086,7 +65086,7 @@
       </c>
       <c r="D626" s="14" t="n">
         <f aca="false">$D$624*D625</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E626" s="14" t="n">
         <f aca="false">$D$624*E625</f>
@@ -65098,7 +65098,7 @@
       </c>
       <c r="G626" s="14" t="n">
         <f aca="false">$D$624*G625</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
     </row>
     <row r="627" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65122,7 +65122,7 @@
       </c>
       <c r="F627" s="19" t="n">
         <f aca="false">F623*F626</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="G627" s="19" t="n">
         <f aca="false">G623*G626</f>
@@ -65143,7 +65143,7 @@
       </c>
       <c r="D629" s="22" t="n">
         <f aca="false">a26_air/D619</f>
-        <v>2.02106868156909</v>
+        <v>2.0210686815691</v>
       </c>
     </row>
     <row r="630" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65187,15 +65187,15 @@
       </c>
       <c r="E631" s="19" t="n">
         <f aca="false">E619*$D$629*E630</f>
-        <v>63.1282305747745</v>
+        <v>63.1282305747746</v>
       </c>
       <c r="F631" s="19" t="n">
         <f aca="false">F619*$D$629*F630</f>
-        <v>69.3527491354094</v>
+        <v>69.3527491354095</v>
       </c>
       <c r="G631" s="19" t="n">
         <f aca="false">G619*$D$629*G630</f>
-        <v>72.926534586915</v>
+        <v>72.9265345869151</v>
       </c>
     </row>
     <row r="632" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65271,7 +65271,7 @@
       </c>
       <c r="E634" s="19" t="n">
         <f aca="false">E627+E631+E632+E633</f>
-        <v>351.307669196166</v>
+        <v>351.307669196167</v>
       </c>
       <c r="F634" s="19" t="n">
         <f aca="false">F627+F631+F632+F633</f>
@@ -65295,7 +65295,7 @@
       </c>
       <c r="E635" s="14" t="n">
         <f aca="false">E634/D634-1</f>
-        <v>0.559978344599226</v>
+        <v>0.559978344599227</v>
       </c>
       <c r="F635" s="14" t="n">
         <f aca="false">F634/E634-1</f>
@@ -65359,7 +65359,7 @@
       </c>
       <c r="G637" s="14" t="n">
         <f aca="false">(G627+G631)/G634</f>
-        <v>0.7360807582572</v>
+        <v>0.736080758257201</v>
       </c>
     </row>
     <row r="638" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65375,7 +65375,7 @@
       </c>
       <c r="E638" s="18" t="n">
         <f aca="false">(E627+E631)/fx/E619*1000</f>
-        <v>178.947189172338</v>
+        <v>178.947189172339</v>
       </c>
       <c r="F638" s="18" t="n">
         <f aca="false">(F627+F631)/fx/F619*1000</f>
@@ -65431,7 +65431,7 @@
       </c>
       <c r="G641" s="19" t="n">
         <f aca="false">$D$640*G634+d_lc*G627</f>
-        <v>158.548016827002</v>
+        <v>158.548016827003</v>
       </c>
     </row>
     <row r="642" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65483,7 +65483,7 @@
       </c>
       <c r="F643" s="19" t="n">
         <f aca="false">E643*(1+MAX(0,phi*F635))</f>
-        <v>19.2249952047764</v>
+        <v>19.2249952047765</v>
       </c>
       <c r="G643" s="19" t="n">
         <f aca="false">F643*(1+MAX(0,phi*G635))</f>
@@ -65515,7 +65515,7 @@
       </c>
       <c r="G644" s="19" t="n">
         <f aca="false">G643+opx_adj_hi*G634</f>
-        <v>29.4665028951675</v>
+        <v>29.4665028951676</v>
       </c>
     </row>
     <row r="645" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65571,7 +65571,7 @@
       </c>
       <c r="G646" s="14" t="n">
         <f aca="false">G645/G634</f>
-        <v>0.274911189906326</v>
+        <v>0.274911189906327</v>
       </c>
     </row>
     <row r="647" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65647,15 +65647,15 @@
       </c>
       <c r="E649" s="19" t="n">
         <f aca="false">(E645+E647)*E648</f>
-        <v>63.8452930212195</v>
+        <v>63.8452930212196</v>
       </c>
       <c r="F649" s="19" t="n">
         <f aca="false">(F645+F647)*F648</f>
-        <v>82.2708468876731</v>
+        <v>82.2708468876732</v>
       </c>
       <c r="G649" s="19" t="n">
         <f aca="false">(G645+G647)*G648</f>
-        <v>87.8050219039886</v>
+        <v>87.8050219039887</v>
       </c>
     </row>
     <row r="650" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65703,7 +65703,7 @@
       </c>
       <c r="E651" s="20" t="n">
         <f aca="false">E649/E650</f>
-        <v>162.653397652869</v>
+        <v>162.65339765287</v>
       </c>
       <c r="F651" s="20" t="n">
         <f aca="false">F649/F650</f>
@@ -65727,11 +65727,11 @@
       </c>
       <c r="E652" s="14" t="n">
         <f aca="false">E651/D651-1</f>
-        <v>0.535026404004124</v>
+        <v>0.535026404004125</v>
       </c>
       <c r="F652" s="14" t="n">
         <f aca="false">F651/E651-1</f>
-        <v>0.288596903460522</v>
+        <v>0.288596903460523</v>
       </c>
       <c r="G652" s="14" t="n">
         <f aca="false">G651/F651-1</f>
@@ -65783,7 +65783,7 @@
       </c>
       <c r="D658" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E658" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -65906,7 +65906,7 @@
       </c>
       <c r="D663" s="20" t="n">
         <f aca="false">D660*D661*D662/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E663" s="20" t="n">
         <f aca="false">E660*E661*E662/1000</f>
@@ -65954,7 +65954,7 @@
       </c>
       <c r="D665" s="14" t="n">
         <f aca="false">a26_lcLL/D664</f>
-        <v>0.436561685977092</v>
+        <v>0.436561685977093</v>
       </c>
       <c r="H665" s="8" t="s">
         <v>468</v>
@@ -65993,11 +65993,11 @@
       </c>
       <c r="D667" s="14" t="n">
         <f aca="false">$D$665*D666</f>
-        <v>0.436561685977092</v>
+        <v>0.436561685977093</v>
       </c>
       <c r="E667" s="14" t="n">
         <f aca="false">$D$665*E666</f>
-        <v>0.414733601678237</v>
+        <v>0.414733601678238</v>
       </c>
       <c r="F667" s="14" t="n">
         <f aca="false">$D$665*F666</f>
@@ -66005,7 +66005,7 @@
       </c>
       <c r="G667" s="14" t="n">
         <f aca="false">$D$665*G666</f>
-        <v>0.371077433080528</v>
+        <v>0.371077433080529</v>
       </c>
     </row>
     <row r="668" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66029,7 +66029,7 @@
       </c>
       <c r="F668" s="19" t="n">
         <f aca="false">F664*F667</f>
-        <v>221.778848938324</v>
+        <v>221.778848938325</v>
       </c>
       <c r="G668" s="19" t="n">
         <f aca="false">G664*G667</f>
@@ -66094,15 +66094,15 @@
       </c>
       <c r="E672" s="19" t="n">
         <f aca="false">E660*$D$670*E671</f>
-        <v>70.3428854976059</v>
+        <v>70.342885497606</v>
       </c>
       <c r="F672" s="19" t="n">
         <f aca="false">F660*$D$670*F671</f>
-        <v>77.2787776080276</v>
+        <v>77.2787776080277</v>
       </c>
       <c r="G672" s="19" t="n">
         <f aca="false">G660*$D$670*G671</f>
-        <v>81.2609956825625</v>
+        <v>81.2609956825626</v>
       </c>
     </row>
     <row r="673" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66186,7 +66186,7 @@
       </c>
       <c r="G675" s="19" t="n">
         <f aca="false">G668+G672+G673+G674</f>
-        <v>448.118110075981</v>
+        <v>448.118110075982</v>
       </c>
     </row>
     <row r="676" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66202,7 +66202,7 @@
       </c>
       <c r="E676" s="14" t="n">
         <f aca="false">E675/D675-1</f>
-        <v>0.511962695697736</v>
+        <v>0.511962695697738</v>
       </c>
       <c r="F676" s="14" t="n">
         <f aca="false">F675/E675-1</f>
@@ -66210,7 +66210,7 @@
       </c>
       <c r="G676" s="14" t="n">
         <f aca="false">G675/F675-1</f>
-        <v>0.0619171161415131</v>
+        <v>0.0619171161415133</v>
       </c>
     </row>
     <row r="677" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66230,7 +66230,7 @@
       </c>
       <c r="E677" s="14" t="n">
         <f aca="false">E668/E675</f>
-        <v>0.450623409860418</v>
+        <v>0.450623409860419</v>
       </c>
       <c r="F677" s="14" t="n">
         <f aca="false">F668/F675</f>
@@ -66262,7 +66262,7 @@
       </c>
       <c r="F678" s="14" t="n">
         <f aca="false">(F668+F672)/F675</f>
-        <v>0.708684619526715</v>
+        <v>0.708684619526716</v>
       </c>
       <c r="G678" s="14" t="n">
         <f aca="false">(G668+G672)/G675</f>
@@ -66442,7 +66442,7 @@
       </c>
       <c r="E686" s="19" t="n">
         <f aca="false">E682-E685</f>
-        <v>97.2327639864483</v>
+        <v>97.2327639864484</v>
       </c>
       <c r="F686" s="19" t="n">
         <f aca="false">F682-F685</f>
@@ -66450,7 +66450,7 @@
       </c>
       <c r="G686" s="19" t="n">
         <f aca="false">G682-G685</f>
-        <v>131.723642093235</v>
+        <v>131.723642093236</v>
       </c>
     </row>
     <row r="687" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66558,11 +66558,11 @@
       </c>
       <c r="F690" s="19" t="n">
         <f aca="false">(F686+F688)*F689</f>
-        <v>84.0669765853071</v>
+        <v>84.0669765853072</v>
       </c>
       <c r="G690" s="19" t="n">
         <f aca="false">(G686+G688)*G689</f>
-        <v>89.5884584129339</v>
+        <v>89.588458412934</v>
       </c>
     </row>
     <row r="691" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66634,7 +66634,7 @@
       </c>
       <c r="E693" s="14" t="n">
         <f aca="false">E692/D692-1</f>
-        <v>0.594215776016352</v>
+        <v>0.594215776016354</v>
       </c>
       <c r="F693" s="14" t="n">
         <f aca="false">F692/E692-1</f>
@@ -66642,7 +66642,7 @@
       </c>
       <c r="G693" s="14" t="n">
         <f aca="false">G692/F692-1</f>
-        <v>0.065679557561154</v>
+        <v>0.0656795575611542</v>
       </c>
     </row>
     <row r="696" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66690,7 +66690,7 @@
       </c>
       <c r="D699" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E699" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -66813,7 +66813,7 @@
       </c>
       <c r="D704" s="20" t="n">
         <f aca="false">D701*D702*D703/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E704" s="20" t="n">
         <f aca="false">E701*E702*E703/1000</f>
@@ -66861,7 +66861,7 @@
       </c>
       <c r="D706" s="14" t="n">
         <f aca="false">a26_lcLH/D705</f>
-        <v>0.545702107471365</v>
+        <v>0.545702107471366</v>
       </c>
       <c r="H706" s="8" t="s">
         <v>468</v>
@@ -66900,7 +66900,7 @@
       </c>
       <c r="D708" s="14" t="n">
         <f aca="false">$D$706*D707</f>
-        <v>0.545702107471365</v>
+        <v>0.545702107471366</v>
       </c>
       <c r="E708" s="14" t="n">
         <f aca="false">$D$706*E707</f>
@@ -66908,11 +66908,11 @@
       </c>
       <c r="F708" s="14" t="n">
         <f aca="false">$D$706*F707</f>
-        <v>0.491131896724228</v>
+        <v>0.491131896724229</v>
       </c>
       <c r="G708" s="14" t="n">
         <f aca="false">$D$706*G707</f>
-        <v>0.46384679135066</v>
+        <v>0.463846791350661</v>
       </c>
     </row>
     <row r="709" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66936,7 +66936,7 @@
       </c>
       <c r="F709" s="19" t="n">
         <f aca="false">F705*F708</f>
-        <v>277.223561172905</v>
+        <v>277.223561172906</v>
       </c>
       <c r="G709" s="19" t="n">
         <f aca="false">G705*G708</f>
@@ -67001,15 +67001,15 @@
       </c>
       <c r="E713" s="19" t="n">
         <f aca="false">E701*$D$711*E712</f>
-        <v>57.717239382651</v>
+        <v>57.7172393826511</v>
       </c>
       <c r="F713" s="19" t="n">
         <f aca="false">F701*$D$711*F712</f>
-        <v>63.4082277809457</v>
+        <v>63.4082277809458</v>
       </c>
       <c r="G713" s="19" t="n">
         <f aca="false">G701*$D$711*G712</f>
-        <v>66.6756887651794</v>
+        <v>66.6756887651795</v>
       </c>
     </row>
     <row r="714" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67089,11 +67089,11 @@
       </c>
       <c r="F716" s="19" t="n">
         <f aca="false">F709+F713+F714+F715</f>
-        <v>456.345223672391</v>
+        <v>456.345223672392</v>
       </c>
       <c r="G716" s="19" t="n">
         <f aca="false">G709+G713+G714+G715</f>
-        <v>485.604595729725</v>
+        <v>485.604595729726</v>
       </c>
     </row>
     <row r="717" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67109,7 +67109,7 @@
       </c>
       <c r="E717" s="14" t="n">
         <f aca="false">E716/D716-1</f>
-        <v>0.595990081275343</v>
+        <v>0.595990081275345</v>
       </c>
       <c r="F717" s="14" t="n">
         <f aca="false">F716/E716-1</f>
@@ -67117,7 +67117,7 @@
       </c>
       <c r="G717" s="14" t="n">
         <f aca="false">G716/F716-1</f>
-        <v>0.0641167487672434</v>
+        <v>0.0641167487672432</v>
       </c>
     </row>
     <row r="718" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67185,7 +67185,7 @@
       </c>
       <c r="D720" s="18" t="n">
         <f aca="false">(D709+D713)/fx/D701*1000</f>
-        <v>163.008813305126</v>
+        <v>163.008813305127</v>
       </c>
       <c r="E720" s="18" t="n">
         <f aca="false">(E709+E713)/fx/E701*1000</f>
@@ -67461,15 +67461,15 @@
       </c>
       <c r="E731" s="19" t="n">
         <f aca="false">(E727+E729)*E730</f>
-        <v>70.2755782628345</v>
+        <v>70.2755782628346</v>
       </c>
       <c r="F731" s="19" t="n">
         <f aca="false">(F727+F729)*F730</f>
-        <v>91.3164760740962</v>
+        <v>91.3164760740963</v>
       </c>
       <c r="G731" s="19" t="n">
         <f aca="false">(G727+G729)*G730</f>
-        <v>97.5161208855515</v>
+        <v>97.5161208855516</v>
       </c>
     </row>
     <row r="732" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67541,15 +67541,15 @@
       </c>
       <c r="E734" s="14" t="n">
         <f aca="false">E733/D733-1</f>
-        <v>0.689629150174879</v>
+        <v>0.689629150174881</v>
       </c>
       <c r="F734" s="14" t="n">
         <f aca="false">F733/E733-1</f>
-        <v>0.299405545018321</v>
+        <v>0.299405545018322</v>
       </c>
       <c r="G734" s="14" t="n">
         <f aca="false">G733/F733-1</f>
-        <v>0.067891853452873</v>
+        <v>0.0678918534528727</v>
       </c>
     </row>
     <row r="737" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67597,7 +67597,7 @@
       </c>
       <c r="D740" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E740" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -67720,7 +67720,7 @@
       </c>
       <c r="D745" s="20" t="n">
         <f aca="false">D742*D743*D744/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E745" s="20" t="n">
         <f aca="false">E742*E743*E744/1000</f>
@@ -67768,7 +67768,7 @@
       </c>
       <c r="D747" s="14" t="n">
         <f aca="false">a26_lc/D746</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H747" s="8" t="s">
         <v>468</v>
@@ -67807,7 +67807,7 @@
       </c>
       <c r="D749" s="14" t="n">
         <f aca="false">$D$747*D748</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E749" s="14" t="n">
         <f aca="false">$D$747*E748</f>
@@ -67819,7 +67819,7 @@
       </c>
       <c r="G749" s="14" t="n">
         <f aca="false">$D$747*G748</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
     </row>
     <row r="750" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67843,7 +67843,7 @@
       </c>
       <c r="F750" s="19" t="n">
         <f aca="false">F746*F749</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="G750" s="19" t="n">
         <f aca="false">G746*G749</f>
@@ -67864,7 +67864,7 @@
       </c>
       <c r="D752" s="22" t="n">
         <f aca="false">a26_airL/D742</f>
-        <v>1.34737912104606</v>
+        <v>1.34737912104607</v>
       </c>
     </row>
     <row r="753" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67912,11 +67912,11 @@
       </c>
       <c r="F754" s="19" t="n">
         <f aca="false">F742*$D$752*F753</f>
-        <v>46.2351660902729</v>
+        <v>46.235166090273</v>
       </c>
       <c r="G754" s="19" t="n">
         <f aca="false">G742*$D$752*G753</f>
-        <v>48.61768972461</v>
+        <v>48.6176897246101</v>
       </c>
     </row>
     <row r="755" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67992,11 +67992,11 @@
       </c>
       <c r="E757" s="19" t="n">
         <f aca="false">E750+E754+E755+E756</f>
-        <v>347.290072131241</v>
+        <v>347.290072131242</v>
       </c>
       <c r="F757" s="19" t="n">
         <f aca="false">F750+F754+F755+F756</f>
-        <v>436.550510028372</v>
+        <v>436.550510028373</v>
       </c>
       <c r="G757" s="19" t="n">
         <f aca="false">G750+G754+G755+G756</f>
@@ -68016,7 +68016,7 @@
       </c>
       <c r="E758" s="14" t="n">
         <f aca="false">E757/D757-1</f>
-        <v>0.542138243263127</v>
+        <v>0.542138243263129</v>
       </c>
       <c r="F758" s="14" t="n">
         <f aca="false">F757/E757-1</f>
@@ -68024,7 +68024,7 @@
       </c>
       <c r="G758" s="14" t="n">
         <f aca="false">G757/F757-1</f>
-        <v>0.0632884202528707</v>
+        <v>0.063288420252871</v>
       </c>
     </row>
     <row r="759" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68080,7 +68080,7 @@
       </c>
       <c r="G760" s="14" t="n">
         <f aca="false">(G750+G754)/G757</f>
-        <v>0.692210714838277</v>
+        <v>0.692210714838278</v>
       </c>
     </row>
     <row r="761" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68144,11 +68144,11 @@
       </c>
       <c r="E764" s="19" t="n">
         <f aca="false">$D$763*E757+d_lc*E750</f>
-        <v>115.688145442066</v>
+        <v>115.688145442067</v>
       </c>
       <c r="F764" s="19" t="n">
         <f aca="false">$D$763*F757+d_lc*F750</f>
-        <v>147.404574113546</v>
+        <v>147.404574113547</v>
       </c>
       <c r="G764" s="19" t="n">
         <f aca="false">$D$763*G757+d_lc*G750</f>
@@ -68208,7 +68208,7 @@
       </c>
       <c r="G766" s="19" t="n">
         <f aca="false">F766*(1+MAX(0,phi*G758))</f>
-        <v>19.8958860947437</v>
+        <v>19.8958860947438</v>
       </c>
     </row>
     <row r="767" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68236,7 +68236,7 @@
       </c>
       <c r="G767" s="19" t="n">
         <f aca="false">G766+0*G757</f>
-        <v>19.8958860947437</v>
+        <v>19.8958860947438</v>
       </c>
     </row>
     <row r="768" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68256,11 +68256,11 @@
       </c>
       <c r="E768" s="19" t="n">
         <f aca="false">E764-E767</f>
-        <v>99.5413290133875</v>
+        <v>99.5413290133876</v>
       </c>
       <c r="F768" s="19" t="n">
         <f aca="false">F764-F767</f>
-        <v>128.352721190859</v>
+        <v>128.35272119086</v>
       </c>
       <c r="G768" s="19" t="n">
         <f aca="false">G764-G767</f>
@@ -68372,11 +68372,11 @@
       </c>
       <c r="F772" s="19" t="n">
         <f aca="false">(F768+F770)*F771</f>
-        <v>87.3130868038301</v>
+        <v>87.3130868038302</v>
       </c>
       <c r="G772" s="19" t="n">
         <f aca="false">(G768+G770)*G771</f>
-        <v>93.1696093061806</v>
+        <v>93.1696093061807</v>
       </c>
     </row>
     <row r="773" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68448,15 +68448,15 @@
       </c>
       <c r="E775" s="14" t="n">
         <f aca="false">E774/D774-1</f>
-        <v>0.631681389693006</v>
+        <v>0.631681389693007</v>
       </c>
       <c r="F775" s="14" t="n">
         <f aca="false">F774/E774-1</f>
-        <v>0.286562674874086</v>
+        <v>0.286562674874087</v>
       </c>
       <c r="G775" s="14" t="n">
         <f aca="false">G774/F774-1</f>
-        <v>0.0670749679885736</v>
+        <v>0.0670749679885732</v>
       </c>
     </row>
     <row r="778" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68504,7 +68504,7 @@
       </c>
       <c r="D781" s="20" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E781" s="20" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -68627,7 +68627,7 @@
       </c>
       <c r="D786" s="20" t="n">
         <f aca="false">D783*D784*D785/1000</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E786" s="20" t="n">
         <f aca="false">E783*E784*E785/1000</f>
@@ -68675,7 +68675,7 @@
       </c>
       <c r="D788" s="14" t="n">
         <f aca="false">a26_lc/D787</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="H788" s="8" t="s">
         <v>468</v>
@@ -68714,7 +68714,7 @@
       </c>
       <c r="D790" s="14" t="n">
         <f aca="false">$D$788*D789</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="E790" s="14" t="n">
         <f aca="false">$D$788*E789</f>
@@ -68726,7 +68726,7 @@
       </c>
       <c r="G790" s="14" t="n">
         <f aca="false">$D$788*G789</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
     </row>
     <row r="791" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68750,7 +68750,7 @@
       </c>
       <c r="F791" s="19" t="n">
         <f aca="false">F787*F790</f>
-        <v>253.461541643799</v>
+        <v>253.4615416438</v>
       </c>
       <c r="G791" s="19" t="n">
         <f aca="false">G787*G790</f>
@@ -68815,15 +68815,15 @@
       </c>
       <c r="E795" s="19" t="n">
         <f aca="false">E783*$D$793*E794</f>
-        <v>84.1709740996993</v>
+        <v>84.1709740996995</v>
       </c>
       <c r="F795" s="19" t="n">
         <f aca="false">F783*$D$793*F794</f>
-        <v>92.4703321805458</v>
+        <v>92.4703321805459</v>
       </c>
       <c r="G795" s="19" t="n">
         <f aca="false">G783*$D$793*G794</f>
-        <v>97.23537944922</v>
+        <v>97.2353794492202</v>
       </c>
     </row>
     <row r="796" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68923,7 +68923,7 @@
       </c>
       <c r="E799" s="14" t="n">
         <f aca="false">E798/D798-1</f>
-        <v>0.577818445935324</v>
+        <v>0.577818445935326</v>
       </c>
       <c r="F799" s="14" t="n">
         <f aca="false">F798/E798-1</f>
@@ -68955,7 +68955,7 @@
       </c>
       <c r="F800" s="14" t="n">
         <f aca="false">F791/F798</f>
-        <v>0.567418566220725</v>
+        <v>0.567418566220726</v>
       </c>
       <c r="G800" s="14" t="n">
         <f aca="false">G791/G798</f>
@@ -68979,7 +68979,7 @@
       </c>
       <c r="E801" s="14" t="n">
         <f aca="false">(E791+E795)/E798</f>
-        <v>0.730387231119088</v>
+        <v>0.730387231119089</v>
       </c>
       <c r="F801" s="14" t="n">
         <f aca="false">(F791+F795)/F798</f>
@@ -68999,7 +68999,7 @@
       </c>
       <c r="D802" s="18" t="n">
         <f aca="false">(D791+D795)/fx/D783*1000</f>
-        <v>180.452560854383</v>
+        <v>180.452560854384</v>
       </c>
       <c r="E802" s="18" t="n">
         <f aca="false">(E791+E795)/fx/E783*1000</f>
@@ -69275,15 +69275,15 @@
       </c>
       <c r="E813" s="19" t="n">
         <f aca="false">(E809+E811)*E812</f>
-        <v>69.3104960266989</v>
+        <v>69.310496026699</v>
       </c>
       <c r="F813" s="19" t="n">
         <f aca="false">(F809+F811)*F812</f>
-        <v>89.1523880066324</v>
+        <v>89.1523880066325</v>
       </c>
       <c r="G813" s="19" t="n">
         <f aca="false">(G809+G811)*G812</f>
-        <v>95.1179854838123</v>
+        <v>95.1179854838124</v>
       </c>
     </row>
     <row r="814" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69355,15 +69355,15 @@
       </c>
       <c r="E816" s="14" t="n">
         <f aca="false">E815/D815-1</f>
-        <v>0.666425768305974</v>
+        <v>0.666425768305976</v>
       </c>
       <c r="F816" s="14" t="n">
         <f aca="false">F815/E815-1</f>
-        <v>0.28627542893778</v>
+        <v>0.286275428937779</v>
       </c>
       <c r="G816" s="14" t="n">
         <f aca="false">G815/F815-1</f>
-        <v>0.0669146122786533</v>
+        <v>0.0669146122786535</v>
       </c>
     </row>
     <row r="819" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69408,7 +69408,7 @@
       </c>
       <c r="E821" s="18" t="n">
         <f aca="false">tp_w_dcf*C821+(1-tp_w_dcf)*D821</f>
-        <v>3965.52216912282</v>
+        <v>3965.52216912283</v>
       </c>
       <c r="F821" s="14" t="n">
         <f aca="false">E821/E$821-1</f>
@@ -69456,11 +69456,11 @@
       </c>
       <c r="E823" s="18" t="n">
         <f aca="false">tp_w_dcf*C823+(1-tp_w_dcf)*D823</f>
-        <v>4251.3644456452</v>
+        <v>4251.36444564521</v>
       </c>
       <c r="F823" s="14" t="n">
         <f aca="false">E823/E$821-1</f>
-        <v>0.0720818758114792</v>
+        <v>0.072081875811479</v>
       </c>
     </row>
     <row r="824" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69484,7 +69484,7 @@
       </c>
       <c r="F824" s="14" t="n">
         <f aca="false">E824/E$821-1</f>
-        <v>0.0439098909482429</v>
+        <v>0.0439098909482432</v>
       </c>
     </row>
     <row r="825" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69508,7 +69508,7 @@
       </c>
       <c r="F825" s="14" t="n">
         <f aca="false">E825/E$821-1</f>
-        <v>-0.0305522424222244</v>
+        <v>-0.0305522424222243</v>
       </c>
     </row>
     <row r="826" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/avc/dist/20261025_奇鋐模型_v0.2.1.xlsx
+++ b/avc/dist/20261025_奇鋐模型_v0.2.1.xlsx
@@ -9799,324 +9799,419 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">）。行業情境：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝高值、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝基準、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝低值（奇鋐、雙鴻模型與本庫 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rack </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁相同）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">lpen_27</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">液冷滲透率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（部署 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中液冷占比）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">lpen_28</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">液冷滲透率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（部署 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中液冷占比）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">lpen_29</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">液冷滲透率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2029</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（部署 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中液冷占比）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">rel_27</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">奇鋐液冷份額 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 ÷ 2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（相對值）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">凱基 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-08-05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（網址見 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Sources</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：奇鋐為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CSP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與企業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GPU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ASIC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">伺服器氣冷與液冷領導廠（未給份額，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Interested-party</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">lpen_27</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">液冷滲透率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（部署 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中液冷占比）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">lpen_28</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">液冷滲透率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2028</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（部署 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中液冷占比）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">lpen_29</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">液冷滲透率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2029</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（部署 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中液冷占比）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">rel_27</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐液冷份額 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 ÷ 2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（相對值）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">凱基 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-08-05</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（網址見 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Sources</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）：奇鋐為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CSP </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">與企業 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GPU</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ASIC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">伺服器氣冷與液冷領導廠（未給份額，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Interested-party</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -10219,7 +10314,64 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）；份額數字：未找到</t>
+      <t xml:space="preserve">）；份額數字：未找到。雙鴻模型的份額相對值取同一組值（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">高、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基準、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">低）</t>
     </r>
   </si>
   <si>

--- a/avc/dist/20261025_奇鋐模型_v0.2.1.xlsx
+++ b/avc/dist/20261025_奇鋐模型_v0.2.1.xlsx
@@ -8546,26 +8546,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">delta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台達電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">delta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台達電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/avc/dist/20261025_奇鋐模型_v0.2.1.xlsx
+++ b/avc/dist/20261025_奇鋐模型_v0.2.1.xlsx
@@ -7551,26 +7551,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7769,26 +7769,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7890,26 +7890,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8011,26 +8011,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8132,26 +8132,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8253,26 +8253,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
